--- a/results/Int Task Remove ACC -0.9/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.00036674816625921204 +/- 0.0007585375089236422</t>
+          <t>0.001039119804401001 +/- 0.0008557457212714099</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.004889975550122261 +/- 0.0017396392996036206</t>
+          <t>-0.00039731051344741306 +/- 0.0012678770484530302</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.0001833740831295394 +/- 0.001283618581907085</t>
+          <t>0.001619804400978031 +/- 0.0008541068834035431</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-9.16870415647586e-05 +/- 0.000761609767382457</t>
+          <t>0.0003973105134474353 +/- 0.000761609767382457</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.002964547677261642 +/- 0.002229376066605981</t>
+          <t>0.00018337408312958382 +/- 0.0008983458714363745</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.002322738386308032 +/- 0.0026964235941458387</t>
+          <t>0.001191931540342328 +/- 0.001590710718786454</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.0002367349233622965</t>
+          <t>-0.00015281173594131615 +/- 0.0003131708669303101</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.002108801955990247 +/- 0.001846178277571997</t>
+          <t>-0.000916870415647919 +/- 0.0005467158869192666</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.007426650366748178 +/- 0.001966705445378512</t>
+          <t>0.013386308068459673 +/- 0.002840161407210016</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.012591687041564825 +/- 0.002592580691986365</t>
+          <t>0.016595354523227402 +/- 0.0026680421468493194</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0016809290953544776 +/- 0.0019581379559463707</t>
+          <t>0.0033312958435208094 +/- 0.0017095802287221335</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.004309290953545253 +/- 0.002175944683536367</t>
+          <t>0.0077933985330073344 +/- 0.001319854699369755</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.008832518337408345 +/- 0.0022310513447432964</t>
+          <t>0.009504889975550124 +/- 0.0014364303178484295</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.007487775061124724 +/- 0.0028969816594032905</t>
+          <t>0.014792176039119819 +/- 0.0021919830167532127</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.00525672371638145 +/- 0.0026425386700754433</t>
+          <t>0.013508557457212722 +/- 0.0019271250330604422</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0004584352078240039 +/- 0.0010520730121062658</t>
+          <t>-0.0017726161369193139 +/- 0.0009837088593784103</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.000458435207823904 +/- 0.0016358708668792977</t>
+          <t>0.004523227383863115 +/- 0.0011581476357882946</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.0028728606356967943 +/- 0.0014348037401351469</t>
+          <t>0.0022616136919315745 +/- 0.0014282789053237102</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.002628361858190753 +/- 0.0009489104337567171</t>
+          <t>0.0012224938875305847 +/- 0.001191539650954651</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-9.16870415647586e-05 +/- 0.00019569450603398585</t>
+          <t>3.0562347188278774e-05 +/- 0.0002883246067254557</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.008924205378973116 +/- 0.0025853650345423846</t>
+          <t>0.019590464547677267 +/- 0.001978071042210811</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.007610024449877728 +/- 0.0012335229872011174</t>
+          <t>-0.006204156479217582 +/- 0.001076645168325717</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0042787286063569515 +/- 0.0015583800469415546</t>
+          <t>0.0007029339853300898 +/- 0.0006975985458748965</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.002658924205378943 +/- 0.0007366730313688261</t>
+          <t>0.0009168704156479301 +/- 0.0008200738303788894</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.002567237163814151 +/- 0.0010516290057509404</t>
+          <t>0.0022310513447432955 +/- 0.0014075279877346727</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.000702933985330112 +/- 0.00047445521687837006</t>
+          <t>0.0001833740831295949 +/- 0.00039138901206801327</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0009168704156479413 +/- 0.0026538255924318404</t>
+          <t>0.005195599022004916 +/- 0.0011993531094345047</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0028422982885085825 +/- 0.0015765550582553748</t>
+          <t>0.00320904645476775 +/- 0.0007998931741016148</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.008893643031784826 +/- 0.0011225163613818357</t>
+          <t>-0.003973105134474309 +/- 0.0008086037014256075</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0054095354523227114 +/- 0.0015284229523288612</t>
+          <t>-0.003422982885085568 +/- 0.0010744740728145948</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0009474327628361423 +/- 0.0005709517632111661</t>
+          <t>6.112469437653534e-05 +/- 0.00040545535334416186</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.0008863080684596402 +/- 0.0007160986866662522</t>
+          <t>-0.0004889975550122161 +/- 0.0003667481662591621</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.007640586797065996 +/- 0.0023074066122465505</t>
+          <t>-0.005073349633251822 +/- 0.0009489104337567049</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.007762836185819089 +/- 0.001051629005750945</t>
+          <t>6.112469437652424e-05 +/- 0.0010744740728146193</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0006112469437652534 +/- 0.000937023821317585</t>
+          <t>-0.00024449877750611917 +/- 0.000405455353344192</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.0013447432762835776 +/- 0.000725815530992531</t>
+          <t>-0.001069682151589224 +/- 0.0004375862183152778</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0002750611246944201 +/- 0.0016024115805523534</t>
+          <t>0.0003361858190709333 +/- 0.001423365650635106</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.0062652811735941175 +/- 0.0016641752310589107</t>
+          <t>-0.0033618581907090437 +/- 0.0007969685091934741</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.00012224938875300407 +/- 0.0008665921075035367</t>
+          <t>-0.000580684596577019 +/- 0.0006330169675185723</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0016503667481662764 +/- 0.00103371237929632</t>
+          <t>-1.1102230246251566e-17 +/- 0.0006554893211958246</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0032090464547676945 +/- 0.0009395126007909465</t>
+          <t>-0.004828850855745692 +/- 0.0010300916593125138</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0012530562347188635 +/- 0.001442918292678844</t>
+          <t>0.002383863080684634 +/- 0.0006233520187766193</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.00690709046454766 +/- 0.0017136730768797397</t>
+          <t>-0.0030562347188264004 +/- 0.0011915396509546367</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.004370415647921733 +/- 0.001207502827942475</t>
+          <t>0.0032396088019560065 +/- 0.0019046988326262748</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0014364303178484362 +/- 0.0007366730313688141</t>
+          <t>0.002017114914425455 +/- 0.0007634471880682802</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.00400366748166262 +/- 0.0007785904158225641</t>
+          <t>0.0003973105134474464 +/- 0.0011997424466008934</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0004889975550121828 +/- 0.0007258155309925225</t>
+          <t>0.00015281173594132723 +/- 0.0004584352078239595</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0004584352078239151 +/- 0.0005509705494290819</t>
+          <t>-0.0007640586797066029 +/- 0.0009091977249782018</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.003361858190709077 +/- 0.0009168704156479228</t>
+          <t>0.004156479217603948 +/- 0.0010427091753809098</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0028117359413203256 +/- 0.0015146102314625694</t>
+          <t>0.002964547677261642 +/- 0.0009860798169255241</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0006723716381418554 +/- 0.001575073193976166</t>
+          <t>0.003911980440097829 +/- 0.0011170945527198685</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.0007640586797066362 +/- 0.0004975189668734706</t>
+          <t>-0.0007640586797065807 +/- 0.0005337484473280246</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.0002750611246943424 +/- 0.0005012597636569846</t>
+          <t>0.0 +/- 0.0005293553812863109</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.00024449877750614134 +/- 0.00018337408312960602</t>
+          <t>-0.00027506112469439793 +/- 0.00016458327650166254</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-0.0005501222493887292 +/- 0.0017862639604159514</t>
+          <t>0.0016503667481662875 +/- 0.0012980905000975088</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.002108801955990158 +/- 0.0011633781363492757</t>
+          <t>0.002322738386308076 +/- 0.001354432750987794</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0007946210268949039 +/- 0.000672371638141818</t>
+          <t>-6.112469437654643e-05 +/- 0.0002994486238121349</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.0006112469437653201 +/- 0.0014593320765664234</t>
+          <t>0.003484107579462137 +/- 0.0006723716381418058</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.0038202933985329703 +/- 0.0014799877766263265</t>
+          <t>0.0016503667481662764 +/- 0.0010154796898432863</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.0016809290953544776 +/- 0.0004584352078239558</t>
+          <t>0.0005806845965770302 +/- 0.000647604526296356</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.0011613691931540604 +/- 0.0016218214133767248</t>
+          <t>0.001436430317848425 +/- 0.0011520829355116781</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.0036063569682151407 +/- 0.001243703542137904</t>
+          <t>-6.112469437652424e-05 +/- 0.001108701537115966</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.0008557457212713504 +/- 0.0012361704410853791</t>
+          <t>0.0031479217603912145 +/- 0.002452806873744914</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.0008251833740830827 +/- 0.001373946625488326</t>
+          <t>-3.056234718824546e-05 +/- 0.0011633781363492933</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-0.00012224938875301516 +/- 0.00034032789503850026</t>
+          <t>-0.00024449877750614134 +/- 0.00012224938875307067</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.001986552567237132 +/- 0.001340917540860633</t>
+          <t>-0.0005806845965769969 +/- 0.0011141641890927846</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.003331295843520743 +/- 0.001062673511657341</t>
+          <t>-0.0016198044009779866 +/- 0.0008541068834035597</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0014058679706601019 +/- 0.0008773044067486185</t>
+          <t>-0.000580684596577008 +/- 0.00021393643031783087</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.0009474327628361423 +/- 0.0010972691363701776</t>
+          <t>-0.00284229828850856 +/- 0.0009474327628361581</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0015586797066014292 +/- 0.0006618706548810389</t>
+          <t>0.0008863080684596957 +/- 0.0012335229872011578</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.0018031784841075372 +/- 0.0015670469123831652</t>
+          <t>-0.0018031784841075816 +/- 0.0009992532227549868</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-0.0002750611246943313 +/- 0.00028832460672543683</t>
+          <t>6.112469437653534e-05 +/- 0.000183374083129606</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.0003667481662592009 +/- 0.0007075694928355722</t>
+          <t>-0.00042787286063570293 +/- 0.0004145678473792753</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0012224938875305292 +/- 0.0007731730220460796</t>
+          <t>-9.168704156480301e-05 +/- 0.0002386995622221142</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0005806845965770635 +/- 0.0005195599022004903</t>
+          <t>-2.2204460492503132e-17 +/- 0.00041003691518945505</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.0017420537897310684 +/- 0.0010591518001933716</t>
+          <t>-0.0010391198044009786 +/- 0.0008665921075035249</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.00027506112469440904 +/- 0.00048226570409718773</t>
+          <t>-0.0007640586797066029 +/- 0.0003416974293245506</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0035452322738385835 +/- 0.0013052662899793793</t>
+          <t>0.0018948655256724068 +/- 0.0006806557900770224</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.0014364303178483694 +/- 0.001297010707452497</t>
+          <t>0.00018337408312958382 +/- 0.001128739933534191</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0019254278728605967 +/- 0.00033618581907089587</t>
+          <t>-0.00018337408312958382 +/- 0.0004965793645865487</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.004003667481662576 +/- 0.0012708204698222542</t>
+          <t>-0.0005195599022004838 +/- 0.0008649738201763557</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.0033007334963324865 +/- 0.0014256606099866407</t>
+          <t>-0.00015281173594133834 +/- 0.0012244025442548958</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.001650366748166221 +/- 0.001395197091749789</t>
+          <t>-0.0005195599022004615 +/- 0.0006120105255043118</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0035387791212031948 +/- 0.0018226525674270063</t>
+          <t>0.004246534945443803 +/- 0.0018519986397059836</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.002654084340902385 +/- 0.0009780668800812257</t>
+          <t>-0.008109702152757314 +/- 0.0012033149963493557</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0017988793866116292 +/- 0.0014771430004562713</t>
+          <t>-0.004335004423473931 +/- 0.0013581337587342335</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0040695959893836675 +/- 0.0016981633794028676</t>
+          <t>0.0005603066941904711 +/- 0.0012817053265762727</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.0020053081686818076 +/- 0.0013565319964612135</t>
+          <t>-0.01347685048658217 +/- 0.002118552056108737</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.008846947803007954 +/- 0.0023145286783071155</t>
+          <t>-0.003273370687112953 +/- 0.002694569816930081</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.846947803008432e-05 +/- 0.00023032290403737036</t>
+          <t>0.000589796520200514 +/- 0.00022842721003878632</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.00014744913005013683 +/- 0.0011516145201867709</t>
+          <t>-0.0021822471247419763 +/- 0.001621672319064282</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.032645237393099394 +/- 0.002230530592432984</t>
+          <t>0.02642288410498376 +/- 0.003107505720393867</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.02087879681509879 +/- 0.0027626159666482852</t>
+          <t>0.02485992332645235 +/- 0.0026012968670009367</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-2.9489826010031805e-05 +/- 0.0014712438434994416</t>
+          <t>-0.000619286346210568 +/- 0.0019581333295233382</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.004924800943674423 +/- 0.0016840214137740267</t>
+          <t>-0.0035387791212032173 +/- 0.0010954984146863275</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.011088174579769983 +/- 0.0024360809705766227</t>
+          <t>0.004335004423473876 +/- 0.002725376903700872</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0048953111176643915 +/- 0.0012244493949883195</t>
+          <t>0.012297257446181032 +/- 0.0013581337587342016</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.004806841639634329 +/- 0.001947445235163562</t>
+          <t>-0.008758478324977902 +/- 0.0022188032209940196</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-8.84694780300621e-05 +/- 0.0016994431771423099</t>
+          <t>-0.002683574166912439 +/- 0.001623012433596808</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.005662046593925119 +/- 0.0014614581767459706</t>
+          <t>-0.001592450604541451 +/- 0.0015163621506555603</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0009436744323208623 +/- 0.0009306832107378097</t>
+          <t>-0.003804187555293459 +/- 0.0008177779194256696</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.0035682689472131936 +/- 0.0010168646210301723</t>
+          <t>-0.00047183721616044226 +/- 0.0008668203159362227</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00014744913005013683 +/- 0.00027188276193728425</t>
+          <t>0.00038336773813031356 +/- 0.0005905333056473178</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.012474196402241244 +/- 0.001396024816106709</t>
+          <t>0.007755824240636944 +/- 0.001498187649174927</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0050132704217045075 +/- 0.0012580789742082795</t>
+          <t>0.0013270421704511647 +/- 0.0012528838564581399</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0022117369507519856 +/- 0.0012248044622409397</t>
+          <t>0.0012680625184311011 +/- 0.0013517153213053231</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0035682689472132157 +/- 0.001175531195989074</t>
+          <t>0.00023591860808018782 +/- 0.0008827266026007391</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.005426127985844886 +/- 0.0015781879280754687</t>
+          <t>0.0015924506045414065 +/- 0.0011884070586617318</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0012385726924211138 +/- 0.0006014767931103131</t>
+          <t>0.0010911235623709437 +/- 0.0006192863462105554</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.010498378059569458 +/- 0.00244321028336278</t>
+          <t>0.009141846063108194 +/- 0.0029430787260099306</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.0010616337363609674 +/- 0.001433824332780099</t>
+          <t>-0.0025066352108522928 +/- 0.0017157402781231268</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.005544087289885003 +/- 0.0008108361595321622</t>
+          <t>-0.00041285756414038977 +/- 0.0011512368797371192</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.00017693895606015752 +/- 0.0014155116484812949</t>
+          <t>-0.009053376585078177 +/- 0.0019295001831855624</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0007372456502506952 +/- 0.0006359144397773008</t>
+          <t>-0.0014744913005013348 +/- 0.0006043615904429022</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.000501327042170463 +/- 0.00035017228213027974</t>
+          <t>0.0006487761722205442 +/- 0.0006567696092987311</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.004541433205544088 +/- 0.0011512368797371513</t>
+          <t>-0.007490415806546758 +/- 0.0024574068600412653</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.005632556767915064 +/- 0.0015235141672768722</t>
+          <t>-0.007519905632556778 +/- 0.001273537179692659</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0007077558242406634 +/- 0.0006213891921470296</t>
+          <t>-0.00017693895606017972 +/- 0.00046064580807470094</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.9489826010031805e-05 +/- 0.0005963948220630072</t>
+          <t>0.00041285756414034537 +/- 0.0007247540977555058</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0051607195517546335 +/- 0.0008968980433940379</t>
+          <t>0.0010911235623709326 +/- 0.0007581810753277749</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.0025656148628723117 +/- 0.0006984794622428213</t>
+          <t>-0.009023886759068133 +/- 0.0014216420870768551</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.00038336773813035796 +/- 0.0006984794622428344</t>
+          <t>-4.4408920985006264e-17 +/- 0.0005595301079625566</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.001592450604541451 +/- 0.0011736802560974571</t>
+          <t>0.0011795930404010391 +/- 0.0014507076232673562</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.006428782070185801 +/- 0.0011927896441260215</t>
+          <t>-0.0010911235623710103 +/- 0.0010472002892695017</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0018873488646417025 +/- 0.0015163621506555484</t>
+          <t>8.8469478030051e-05 +/- 0.001929500183185544</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0017104099085815338 +/- 0.0010112903685922726</t>
+          <t>-0.004600412857564162 +/- 0.0023227801436172552</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.006340312592155695 +/- 0.001415818800844336</t>
+          <t>0.0071660277204363965 +/- 0.0014022404515445267</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.00044234739015039934 +/- 0.0008470307647505343</t>
+          <t>-0.0023886759068121655 +/- 0.0013019015072040078</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.002683574166912428 +/- 0.001130272361942589</t>
+          <t>0.0006487761722205332 +/- 0.0011018308282081607</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.0006782659982306316 +/- 0.0004764227195931582</t>
+          <t>0.00035387791212029287 +/- 0.00028894010531207276</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.00035387791212031504 +/- 0.000902215189665505</t>
+          <t>0.003981126511353561 +/- 0.0014700611714083967</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.010852255971689762 +/- 0.0018548139420249449</t>
+          <t>-0.009230315541138323 +/- 0.0017248397305679405</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.005662046593925085 +/- 0.0013565319964612323</t>
+          <t>-0.017811854910056057 +/- 0.0012594607197913591</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.010498378059569458 +/- 0.0010484452276397155</t>
+          <t>-0.003568268947213238 +/- 0.0012884725611886705</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.0006487761722205998 +/- 0.0005073621508135027</t>
+          <t>0.0006487761722205554 +/- 0.0005868401280487366</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5.897965202005251e-05 +/- 0.0006157656448782655</t>
+          <t>0.0001769389560601242 +/- 0.00035387791212031314</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.0006487761722205887 +/- 0.000615765644878243</t>
+          <t>-3.3306690738754695e-17 +/- 0.0005107787695573294</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.003066941905042764 +/- 0.0016376813184210714</t>
+          <t>-0.010645827189619605 +/- 0.0014292681587794235</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.000589796520200514 +/- 0.0020810709247274825</t>
+          <t>0.00026540843409019745 +/- 0.0018995202495060773</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,107 +1616,107 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.00020642878207018933 +/- 0.0003741839439826108</t>
+          <t>-0.0006487761722205998 +/- 0.0006698800761781472</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.00044234739015041046 +/- 0.0006079483376021331</t>
+          <t>-0.006458271896195844 +/- 0.001853172202107319</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.006045414332055454 +/- 0.0009802872390796073</t>
+          <t>-0.012651135358301424 +/- 0.001815241922325256</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.00026540843409025296 +/- 0.0005816302837899385</t>
+          <t>-0.0010911235623709882 +/- 0.0005756184398685619</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.0025951046888823435 +/- 0.0008526589380596125</t>
+          <t>-0.0016219404305514607 +/- 0.0007009651621353263</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.00778531406664702 +/- 0.000736655617622923</t>
+          <t>-0.014332055440872914 +/- 0.0015106161574598262</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.004010616337363604 +/- 0.0009156104214839285</t>
+          <t>0.004069595989383623 +/- 0.0015140663701555244</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.0007372456502506619 +/- 0.0005786321695767751</t>
+          <t>0.004718372161604212 +/- 0.0009601191740548313</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-0.00011795930404010502 +/- 0.00030073839655518164</t>
+          <t>-0.0006782659982306316 +/- 0.00032438808611029635</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.00872898849896787 +/- 0.0010401174926893632</t>
+          <t>-0.0005013270421704741 +/- 0.001468877547084899</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.0034503096431730993 +/- 0.0011194487110647202</t>
+          <t>0.0019463285166617106 +/- 0.0012385726924210977</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.001209082866411104 +/- 0.00046534160536889317</t>
+          <t>-0.001002654084340926 +/- 0.0005141726857612055</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.03282217634915955 +/- 0.002143040082456412</t>
+          <t>0.006694190504275987 +/- 0.0014084286565920865</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0008748096121611067</t>
+          <t>-0.00014744913005015903 +/- 0.0011740506775225128</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.011795930404010613 +/- 0.001383195446718804</t>
+          <t>0.00011795930404006061 +/- 0.001202953586220633</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>5.897965202006361e-05 +/- 0.0002206816506502276</t>
+          <t>-8.846947803010652e-05 +/- 0.00018882701968248977</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0010026540843409149 +/- 0.0008257151282807597</t>
+          <t>5.89796520200192e-05 +/- 0.0003439075137036378</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0013860218224712507 +/- 0.0005445645919380567</t>
+          <t>0.0006487761722205554 +/- 0.0006157656448782303</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>5.897965202006361e-05 +/- 0.00011795930404012722</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0005603066941905043 +/- 0.00040541807976607303</t>
+          <t>-0.00026540843409027514 +/- 0.0003078828224390992</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.0071955175464464725 +/- 0.0015391316249719622</t>
+          <t>0.001415511648481238 +/- 0.0012497564199597355</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-2.9489826010031805e-05 +/- 0.0003349400380890961</t>
+          <t>-0.0008257151282807685 +/- 0.00031761514639543244</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0017988793866116181 +/- 0.0012473185480717489</t>
+          <t>-0.000973164258330883 +/- 0.0007807845647227111</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.0012385726924211248 +/- 0.0008526589380596278</t>
+          <t>-0.0006782659982306316 +/- 0.001358133758734221</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.00032438808611030546 +/- 0.00044626204513186</t>
+          <t>-0.00020642878207022264 +/- 0.00039674503235251763</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0016219404305514717 +/- 0.0009160852000595296</t>
+          <t>-0.004629902683574216 +/- 0.0011725682897122463</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.0035977587732232363 +/- 0.0014374588743089245</t>
+          <t>0.010439398407549382 +/- 0.0008567289322520556</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0008846947803008099 +/- 0.0009325501799376054</t>
+          <t>0.0016219404305514052 +/- 0.0005934713004275506</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.007073098549866874 +/- 0.001293048373776495</t>
+          <t>-0.0029890500147972455 +/- 0.0013526362689584535</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.016424977804084095 +/- 0.0016005702613779084</t>
+          <t>-0.015122817401598099 +/- 0.0014282247424698283</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.0062444510210121875 +/- 0.0016071232888293114</t>
+          <t>-0.0013613495116898244 +/- 0.0012913539052542783</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.00272269902337976 +/- 0.0010234753753057277</t>
+          <t>-0.005563776265167209 +/- 0.0011136364440501262</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.005800532701982874 +/- 0.000992190270153338</t>
+          <t>-0.004379994081089067 +/- 0.0009707735701010466</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.006510802012429762 +/- 0.001615548276289596</t>
+          <t>-0.0009766203018644394 +/- 0.0016103898029491027</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.00026635099141759656 +/- 0.00020716188221370384</t>
+          <t>-0.000503107428233196 +/- 0.0004781146617757686</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.010713228765907124 +/- 0.0017041941460654588</t>
+          <t>-0.004498372299496889 +/- 0.0008556870254395612</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.01894051494525003 +/- 0.0038903052323539565</t>
+          <t>0.014501331754957103 +/- 0.0023823156907366856</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.01689849067771526 +/- 0.00416947259911664</t>
+          <t>0.01840781296241494 +/- 0.0036982537678161235</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0029298609055933176 +/- 0.00144650481324057</t>
+          <t>-0.0014797277300976353 +/- 0.0010421318059578983</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.006540396567031703 +/- 0.0010542475957713746</t>
+          <t>-0.0008878366380585812 +/- 0.0010251854439590681</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.00446877774489497 +/- 0.0010204758596961442</t>
+          <t>-0.0027818881325835654 +/- 0.0010604600690836898</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.011897010949985165 +/- 0.0017144419482640224</t>
+          <t>0.006362829239419965 +/- 0.0017269126322456527</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.01186741639538319 +/- 0.0022633546972475804</t>
+          <t>0.009884581237052392 +/- 0.0021390128439884855</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.009381473808819218 +/- 0.002154719342914147</t>
+          <t>-0.0074282332050902514 +/- 0.0017778914821989348</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0063332346848180236 +/- 0.0011926275039721961</t>
+          <t>-0.0032849955608167613 +/- 0.00084175570602711</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.002604320804971838 +/- 0.0011446628946915282</t>
+          <t>-0.0009174311926605338 +/- 0.0006934225814655086</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.006007694584196544 +/- 0.0015662762500620686</t>
+          <t>-0.0029890500147972676 +/- 0.0013396235925133492</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-8.878366380586922e-05 +/- 0.00023114086048852707</t>
+          <t>0.0005918910920390541 +/- 0.00037434479552155334</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00029594554601948265 +/- 0.002222549080262641</t>
+          <t>-0.000976620301864428 +/- 0.001674382380564139</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.0009174311926606227 +/- 0.0010707340938221838</t>
+          <t>-0.002604320804971838 +/- 0.001144662894691528</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.002278780704350358 +/- 0.001161751194222561</t>
+          <t>-0.0009766203018644394 +/- 0.0011156008774767933</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0011245930748743026 +/- 0.0006179524420781712</t>
+          <t>-0.00440958863569102 +/- 0.0016394955885723219</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0013021604024858967 +/- 0.001611205396722846</t>
+          <t>-0.003847292098253896 +/- 0.0010251854439591133</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0008878366380585701 +/- 0.0006207806144836799</t>
+          <t>0.00020716188221366893 +/- 0.00039815401145526687</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.006155667357206329 +/- 0.002740653898263442</t>
+          <t>8.878366380589142e-05 +/- 0.0031040441557152504</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.005297425273749656 +/- 0.0015460145470978324</t>
+          <t>-0.0030778336786030924 +/- 0.0012072256912915753</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.002308375258952311 +/- 0.0010897870754378002</t>
+          <t>0.0018348623853211231 +/- 0.0010977944356905492</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0008878366380585479 +/- 0.0014797277300976752</t>
+          <t>0.0013613495116898578 +/- 0.0017418098809780685</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0005031074282332626 +/- 0.0005926304940663532</t>
+          <t>-0.0017460787215152096 +/- 0.00040685785986585587</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.00035513465522341026 +/- 0.0006036128456458109</t>
+          <t>-0.0014501331754956826 +/- 0.0005684928296033796</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.0015981059485055348 +/- 0.0010353865454001874</t>
+          <t>-0.0012429712932820135 +/- 0.0010319973823120674</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.005622965374371081 +/- 0.001610117846550529</t>
+          <t>-0.004764723290914463 +/- 0.001062522821605002</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.0011245930748742029 +/- 0.0004735128736312433</t>
+          <t>-0.0013613495116898244 +/- 0.0004622817209770058</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.00044391831902926835 +/- 0.0007857897630868351</t>
+          <t>0.0013613495116898578 +/- 0.0009921902701533313</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.00023675643681558833 +/- 0.0012471919210243218</t>
+          <t>-0.004498372299496867 +/- 0.0011369856592068027</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0009470257472624644 +/- 0.001361349511689852</t>
+          <t>-0.0029298609055933176 +/- 0.0009585164096301482</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0008582420834566951 +/- 0.000627097369056468</t>
+          <t>-0.0019532406037288787 +/- 0.0006374862157010247</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.00014797277300971913 +/- 0.0010358094110683954</t>
+          <t>-0.003137022787807009 +/- 0.0011852609881326441</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.004320804971885117 +/- 0.001177848401428395</t>
+          <t>-0.001390944066291777 +/- 0.0020548511792648732</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0022491861497484942 +/- 0.0013445181049542012</t>
+          <t>0.00023675643681564384 +/- 0.0018137382001828467</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.0009174311926606005 +/- 0.0011647628679582658</t>
+          <t>-8.878366380585812e-05 +/- 0.0018293648369961896</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.0019532406037289785 +/- 0.0011778484014283723</t>
+          <t>-0.008020124297129306 +/- 0.0017430665075616626</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.0010949985202723168 +/- 0.0012348414350414586</t>
+          <t>-0.0012133767386800609 +/- 0.0011647628679582165</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0009470257472624533 +/- 0.001189686371248428</t>
+          <t>-0.005297425273749612 +/- 0.0015906901036255405</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0006214856466410068 +/- 0.0005528719056605228</t>
+          <t>-0.0005327019828351487 +/- 0.00041432376442733786</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0020716188221366894 +/- 0.0007003349846818003</t>
+          <t>-0.0010358094110683447 +/- 0.0012642799268004405</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.001390944066291766 +/- 0.0013500437677368422</t>
+          <t>-0.0003847292098253741 +/- 0.0014318994262684684</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5.918910920396092e-05 +/- 0.0018661003575536606</t>
+          <t>-0.0005327019828351598 +/- 0.0016887058440588434</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0056229653743710695 +/- 0.0012899967278901326</t>
+          <t>0.0042320213080793475 +/- 0.0007492742764825057</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.00032554010062147977 +/- 0.0004478468763072294</t>
+          <t>-0.0015389168393015406 +/- 0.0009886530386794769</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0006214856466410845 +/- 0.000654434577907581</t>
+          <t>-0.0009174311926605338 +/- 0.000503107428233196</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0032258064516128447 +/- 0.00036124757667160346</t>
+          <t>0.00041432376442733786 +/- 0.0005646281156655391</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0012133767386800609 +/- 0.0009493350063536638</t>
+          <t>-0.0018348623853210676 +/- 0.0014903436889036926</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.00381769754365201 +/- 0.001118736796178482</t>
+          <t>-0.003107428233205056 +/- 0.001527778573440706</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,147 +2061,147 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.00029594554601957145 +/- 0.0004185302049047654</t>
+          <t>-0.0012429712932820135 +/- 0.0005738597049323754</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.005327019828351609 +/- 0.0009725763080884928</t>
+          <t>-0.0032554010062148197 +/- 0.0009635288899733642</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.0012725658478839551 +/- 0.0016951765009315925</t>
+          <t>0.0018940514945250287 +/- 0.0010849542929756643</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0011541876294761555 +/- 0.00036124757667160346</t>
+          <t>-0.0010358094110683447 +/- 0.0007157967814411131</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0026339153595737906 +/- 0.0012656646806950406</t>
+          <t>0.00011837821840782192 +/- 0.0010768514589322533</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.00029594554601958256 +/- 0.0013432146455058188</t>
+          <t>-0.00411364308967147 +/- 0.0015231854669970912</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.0037881029890500574 +/- 0.001040449590485151</t>
+          <t>-0.003551346552234358 +/- 0.0011152082676186492</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-0.00381769754365201 +/- 0.0012794297911344714</t>
+          <t>-0.0026339153595737906 +/- 0.0008312857002182827</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-0.0003847292098254185 +/- 0.00029742159281214087</t>
+          <t>-0.00029594554601952705 +/- 0.0002292384342235778</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.002367564368156316 +/- 0.001375430605341488</t>
+          <t>-0.0027522935779816125 +/- 0.0014501331754956976</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.9189109203861e-05 +/- 0.0015366386488010978</t>
+          <t>-0.0024859425865640383 +/- 0.0011852609881326298</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-2.9594554601974908e-05 +/- 0.0007303322094852536</t>
+          <t>-0.0007694584196507703 +/- 0.0005159986911560337</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.0006214856466410845 +/- 0.0012162605852639797</t>
+          <t>8.878366380588032e-05 +/- 0.0015266315923680351</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0010654039656702863 +/- 0.0010686871906047798</t>
+          <t>-0.004143237644273423 +/- 0.001400669969363643</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.003225806451612856 +/- 0.0010374991502194863</t>
+          <t>-0.003995264871263648 +/- 0.001185630400947644</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-5.918910920391651e-05 +/- 0.00022146536766938887</t>
+          <t>0.00029594554601952705 +/- 0.0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.000976620301864428 +/- 0.0009639832775911418</t>
+          <t>-0.0026339153595737906 +/- 0.000503107428233196</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.001716484166913368 +/- 0.0008956937526144589</t>
+          <t>-0.0021604024859425476 +/- 0.0005302300345418347</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2.9594554601952706e-05 +/- 8.878366380585811e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.00109499852027225 +/- 0.0005776626604303872</t>
+          <t>-0.0007990529742527231 +/- 0.0006214856466410069</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.004054453980467543 +/- 0.0012133767386800977</t>
+          <t>-0.005711749038176961 +/- 0.0015208837120484914</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>5.918910920390541e-05 +/- 0.00011837821840781082</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00038472920982538514 +/- 0.0006214856466410068</t>
+          <t>-0.0005918910920390541 +/- 0.00037434479552155334</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0005327019828351154 +/- 0.0009617091926174845</t>
+          <t>-0.00452796685409883 +/- 0.0017054784888101797</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.00455756140870075 +/- 0.0012569849412012715</t>
+          <t>-0.006717963894643364 +/- 0.0012559393414574103</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.0015981059485054461 +/- 0.0005799324635177588</t>
+          <t>-0.0021899970405445 +/- 0.0005327019828351487</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.000562296537437068 +/- 0.0009943946502759305</t>
+          <t>0.0006806747558449344 +/- 0.0013947169775612017</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.0018940514945250731 +/- 0.001249997755663978</t>
+          <t>-0.0014797277300976353 +/- 0.0015826862334561344</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.00035513465522342137 +/- 0.0011522889809962667</t>
+          <t>-0.005119857946137907 +/- 0.0007835574012946999</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0005022156573116666 +/- 0.0013082180103683551</t>
+          <t>0.0015952732644017643 +/- 0.0012266197631921173</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.0012112259970457838 +/- 0.0011701803438900003</t>
+          <t>0.001004431314623333 +/- 0.0009726486046176805</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.00815361890694235 +/- 0.0013356164910436935</t>
+          <t>-0.002895125553914313 +/- 0.0019452972092353607</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0009453471196454899 +/- 0.0009690528488541588</t>
+          <t>0.003367799113737058 +/- 0.0011456850475429963</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0010930576070900977 +/- 0.0011521418020679407</t>
+          <t>0.0007680945347119606 +/- 0.00104196112783151</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.003545051698670587 +/- 0.0013856471964027784</t>
+          <t>-0.0014180206794682348 +/- 0.0018201384698078914</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.0003783234409118355</t>
+          <t>0.0002067946824224509 +/- 0.0003748471946957003</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.005140324963072351 +/- 0.0010667929149345758</t>
+          <t>-0.002481536189069411 +/- 0.0015247843900223189</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.029955686853766615 +/- 0.0034759388077005232</t>
+          <t>0.02366322008862628 +/- 0.002810228417243465</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.02121122599704579 +/- 0.0019408056373006505</t>
+          <t>0.028478581979320496 +/- 0.002454662106687253</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.002806499261447548 +/- 0.0013682169780690518</t>
+          <t>-0.000531757754800588 +/- 0.00047267355982274497</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.002688330871491862 +/- 0.0010606394724381773</t>
+          <t>-0.004135893648449018 +/- 0.0010974402139442608</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.0009748892171344114 +/- 0.0015353366570382528</t>
+          <t>-0.006085672082717897 +/- 0.0017833250543913578</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.008035450516986665 +/- 0.0017011734178892636</t>
+          <t>-0.016011816838995597 +/- 0.0016384549038537045</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.003958641063515489 +/- 0.0009904315872520015</t>
+          <t>0.005169867060561273 +/- 0.0019111248436792653</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0019497784342688228 +/- 0.0008165598204481643</t>
+          <t>-0.002954209748892156 +/- 0.0008562113291692386</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.004756277695716371 +/- 0.0009838006384252067</t>
+          <t>-0.0018906942392909799 +/- 0.00104196112783151</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0006499261447562743 +/- 0.000854170298067999</t>
+          <t>0.0013589364844903916 +/- 0.0012266197631921173</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.007858197932053135 +/- 0.001478286086049836</t>
+          <t>-0.002067946824224509 +/- 0.0008763602348118906</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.0003249630723781372 +/- 0.000360607256003948</t>
+          <t>0.0002954209748892156 +/- 0.000735592295302137</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.001353788979307479</t>
+          <t>-0.006824224519940925 +/- 0.0011245415840871464</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.001004431314623333 +/- 0.0013742633204860202</t>
+          <t>0.002215657311669117 +/- 0.000738552437223039</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0015952732644017643 +/- 0.0008480177308364696</t>
+          <t>0.0011816838995568624 +/- 0.0012877101753443576</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0007976366322008821 +/- 0.0007361852758863839</t>
+          <t>-0.0007976366322008821 +/- 0.0010655650692390746</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.0004135893648449018 +/- 0.0016083494935085528</t>
+          <t>-0.002127031019202352 +/- 0.0009134194879610178</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.00030842855270045774</t>
+          <t>-0.0005612998522895096 +/- 0.0003840472673559803</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0010930576070900977 +/- 0.0014891678772382267</t>
+          <t>0.004963072378138822 +/- 0.0015676808462536521</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.007267355982274704 +/- 0.0007726261052066146</t>
+          <t>0.005199409158050195 +/- 0.001597460069080733</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0010339734121122546 +/- 0.0012689353970407337</t>
+          <t>-0.0013293943870014702 +/- 0.0008788463681325519</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.002481536189069411 +/- 0.0012822767748425755</t>
+          <t>0.004874446085672057 +/- 0.0009820248235506395</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.0003840472673559803 +/- 0.00039744827317795097</t>
+          <t>-0.00017725258493352935 +/- 0.00019596010578170652</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.00011816838995568624 +/- 0.0005937888107013789</t>
+          <t>-5.908419497784312e-05 +/- 0.000368980679373611</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0030723781388478423 +/- 0.0011380419665735966</t>
+          <t>-5.908419497784312e-05 +/- 0.000721214512007896</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0015657311669128426 +/- 0.0011136234460839389</t>
+          <t>0.004519940915804999 +/- 0.00094396131808983</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.00011816838995568624 +/- 0.0001447261295588281</t>
+          <t>-0.0005022156573116666 +/- 0.000477267191178831</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.0012407680945347055 +/- 0.00028945225911765614</t>
+          <t>-0.0008862629246676468 +/- 0.0004576642063465166</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0001477104874446078 +/- 0.0011908800219052448</t>
+          <t>-0.0049926144756277544 +/- 0.0009568174145171034</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.0004431314623338234 +/- 0.0008984878183601459</t>
+          <t>0.0005908419497784312 +/- 0.001314540352217836</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0023338257016248033 +/- 0.0006794682422451959</t>
+          <t>-0.000738552437223039 +/- 0.00042297846568024454</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0010930576070900977 +/- 0.0008965430372521973</t>
+          <t>-0.0006499261447562743 +/- 0.0010130829069117965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0038404726735598027 +/- 0.0007473625193898642</t>
+          <t>0.002629246676514019 +/- 0.0013631045193570773</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0016248153618906858 +/- 0.001067201882906254</t>
+          <t>-0.000265878877400294 +/- 0.000992632060053847</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0037813884785819598 +/- 0.0008743662385198621</t>
+          <t>0.003131462333825685 +/- 0.0009992044032666278</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.0016543574593796072 +/- 0.0013869063036106872</t>
+          <t>-0.0012112259970457838 +/- 0.0012907564121095044</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0019202363367799014 +/- 0.0013618234058039645</t>
+          <t>-0.0001477104874446078 +/- 0.0006370416145597551</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.002688330871491862 +/- 0.0011167538062886678</t>
+          <t>0.005553914327917253 +/- 0.0013132118623865733</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0004135893648449018 +/- 0.0006224906205525958</t>
+          <t>-0.00047267355982274497 +/- 0.0003545051698670587</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0013589364844903916 +/- 0.0004978522761108605</t>
+          <t>0.003485967503692744 +/- 0.000843891099384675</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.00587887740029539 +/- 0.00116269829566643</t>
+          <t>-0.0030428360413589208 +/- 0.0006061531618517898</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0011816838995568624 +/- 0.001196363765513529</t>
+          <t>-0.0003840472673559803 +/- 0.0006997175351448714</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0018316100443131367 +/- 0.0009690528488541588</t>
+          <t>0.002865583456425391 +/- 0.0012606551428863669</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.00030842855270045774</t>
+          <t>-0.0001477104874446078 +/- 0.0003302906909157722</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.0006499261447562743</t>
+          <t>0.0001477104874446078 +/- 0.00040181596776175395</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>8.862629246676468e-05 +/- 0.0001353788979307479</t>
+          <t>0.000531757754800588 +/- 0.00011816838995568624</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.007976366322008831 +/- 0.0013473269425100746</t>
+          <t>0.0033087149187592145 +/- 0.0009600045382139933</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.0028360413589364696 +/- 0.0013356164910436935</t>
+          <t>0.00023633677991137249 +/- 0.0009416471167213675</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.0001477104874446078 +/- 0.0004624069672820811</t>
+          <t>0.0 +/- 0.0007114679219375027</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0010339734121122546 +/- 0.0007266395200146989</t>
+          <t>0.0029246676514032345 +/- 0.0008607859547612046</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.0029837518463810774 +/- 0.0011850027249708404</t>
+          <t>0.0049335302806499 +/- 0.0010978377652030695</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.0005674851613677532</t>
+          <t>0.000738552437223039 +/- 0.0004624069672820811</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.003279172821270293 +/- 0.000786619022493015</t>
+          <t>0.0008862629246676468 +/- 0.0013602203170719382</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.0023633677991137247 +/- 0.0011668193594169215</t>
+          <t>0.0002954209748892156 +/- 0.0009618210101092834</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.002688330871491862 +/- 0.0011167538062886676</t>
+          <t>0.004608567208271764 +/- 0.0016721975418711767</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.0038109305760708812 +/- 0.0004470530561424365</t>
+          <t>-2.954209748892156e-05 +/- 0.0005826612385026859</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0002707577958614958</t>
+          <t>5.908419497784312e-05 +/- 0.00031817812745255395</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.0025997045790250974 +/- 0.0004538343130202994</t>
+          <t>-0.004017725258493332 +/- 0.0007260387431281798</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.002806499261447548 +/- 0.0008277060990323088</t>
+          <t>0.0008271787296898036 +/- 0.0009508701293607679</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.0005908419497784312 +/- 0.0004763520087620979</t>
+          <t>-0.0008271787296898036 +/- 0.0005415155917229916</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.0039881831610044105 +/- 0.0010589925157420872</t>
+          <t>-0.00490398818316099 +/- 0.0013931847707594307</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.0023633677991137247 +/- 0.0006336074029402394</t>
+          <t>0.000738552437223039 +/- 0.000579657810054608</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.0014180206794682348 +/- 0.0007680945347119606</t>
+          <t>-0.0013884785819793133 +/- 0.00110575877531538</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.00011816838995568624 +/- 0.00019596010578170652</t>
+          <t>0.0004135893648449018 +/- 0.0002707577958614958</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0005908419497784312 +/- 0.0002954209748892156</t>
+          <t>-0.0003249630723781372 +/- 0.0003355337279645639</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0003840472673559803 +/- 0.00018916172045591774</t>
+          <t>0.0005612998522895096 +/- 0.0004061366937922437</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0005612998522895096 +/- 0.0005193026833455495</t>
+          <t>-0.0004135893648449018 +/- 0.0004978522761108605</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0015066469719349994 +/- 0.0011167538062886678</t>
+          <t>0.0024519940915804896 +/- 0.0013346359820474397</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-2.954209748892156e-05 +/- 8.862629246676468e-05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.00030842855270045774</t>
+          <t>-0.0002954209748892156 +/- 0.0002642325527326178</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0012407680945347055 +/- 0.00047267355982274497</t>
+          <t>-0.0005612998522895096 +/- 0.0009568174145170791</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.0002954209748892156 +/- 0.0006864963095197749</t>
+          <t>-0.0027769571639586267 +/- 0.001106942038120833</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0003249630723781372 +/- 0.0006532745757015028</t>
+          <t>-0.0006499261447562743 +/- 0.000657933750408271</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0005612998522895096 +/- 0.0011399575410088413</t>
+          <t>-0.00023633677991137249 +/- 0.0015339149170749899</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.002392909896602646 +/- 0.0008192274519268522</t>
+          <t>-0.002156573116691274 +/- 0.0007242334222824933</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449018 +/- 0.0007726261052066147</t>
+          <t>-0.001683899556868529 +/- 0.00094396131808983</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0020722320899940637 +/- 0.0012061307748646008</t>
+          <t>0.00044404973357013987 +/- 0.0014457211897069054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00127294256956777 +/- 0.002254715692638191</t>
+          <t>-0.006660746003552443 +/- 0.0011711095586058318</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.000769686204854958 +/- 0.0014332407858982008</t>
+          <t>-0.0006512729425695807 +/- 0.0011826515308133766</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.001095322676139754 +/- 0.0010840635537951754</t>
+          <t>-0.0014801657785672218 +/- 0.0013172643849192795</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.000976909413854332 +/- 0.0009081031172396508</t>
+          <t>-0.0012729425695678365 +/- 0.0017566019774004514</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.007756068679692163 +/- 0.0008861237150441656</t>
+          <t>-0.004677323860272387 +/- 0.0016577856719952506</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.00032563647128478477 +/- 0.0003090676882448288</t>
+          <t>0.00014801657785668 +/- 0.00023866956034037206</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.007548845470692689 +/- 0.0010104232188203632</t>
+          <t>-0.0010361160449970709 +/- 0.001318926548842252</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0072528123149793065 +/- 0.002017591380863067</t>
+          <t>-0.005002960331557171 +/- 0.002922943293782637</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.005180580224985232 +/- 0.002232058584504958</t>
+          <t>0.00198342214328 +/- 0.0021143068485102493</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.00885139135583184 +/- 0.0019205685711436908</t>
+          <t>-0.008525754884547099 +/- 0.0017251394060785624</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.00180580224985194 +/- 0.0005686611223297404</t>
+          <t>0.004114860864416803 +/- 0.0013530366941416877</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0010657193605684069 +/- 0.001680884495746413</t>
+          <t>0.0005624629958555172 +/- 0.001272942569567815</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.0033451746595618446 +/- 0.003199487123960728</t>
+          <t>-0.004203670811130877 +/- 0.002214517964388996</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.00932504440497337 +/- 0.002681511398924118</t>
+          <t>0.0077856719952634655 +/- 0.002293254044625736</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.00251628182356427 +/- 0.0014992844596922038</t>
+          <t>0.000917702782711649 +/- 0.0006678812417216448</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.00559502664298398 +/- 0.0013659291882841338</t>
+          <t>5.9206631142660895e-05 +/- 0.0014184900592907948</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.004410894020130218 +/- 0.0014887259870550815</t>
+          <t>-0.012551805802249882 +/- 0.0012712202814436802</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0037300177619893128 +/- 0.001155667335461401</t>
+          <t>-0.00224985198342218 +/- 0.0013119313088312832</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.000444049733570151 +/- 0.00033097512988450605</t>
+          <t>-0.0001480165778567577 +/- 0.00027292908399326925</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0030787448194197543 +/- 0.0017473480832887792</t>
+          <t>-0.009206631142688004 +/- 0.0013594982241805882</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.006127886323268184 +/- 0.001242281542827541</t>
+          <t>-0.006127886323268217 +/- 0.0013242314533063965</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.007075192421551224 +/- 0.001126871895244173</t>
+          <t>0.0028715216104203355 +/- 0.0009642686486028571</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.002072232089994097 +/- 0.001330503555609466</t>
+          <t>0.0015393724097098604 +/- 0.0014966518247204943</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.002782711663706383 +/- 0.0011929805612557831</t>
+          <t>0.0036116044997039688 +/- 0.001335762483443277</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0003256364712847737 +/- 0.00042797016858499184</t>
+          <t>-0.0001480165778567466 +/- 0.0005655705498680388</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.002664298401420995 +/- 0.0026839613870084217</t>
+          <t>0.005269390171699207 +/- 0.0010657193605683802</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.019271758436944907 +/- 0.0022794552989935037</t>
+          <t>-0.018294849023090608 +/- 0.002142102133229793</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.004203670811130844 +/- 0.0011973800127979169</t>
+          <t>-0.00834813499111905 +/- 0.0017899605041836585</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.00044404973357018427 +/- 0.0013122652610598902</t>
+          <t>-0.003197158081705176 +/- 0.0013488201006387885</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-2.9603315571324895e-05 +/- 0.0003848431024274798</t>
+          <t>-0.0001776198934281048 +/- 0.000595019278929581</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0005328596802841923 +/- 0.0005585542410927413</t>
+          <t>0.000621669626998178 +/- 0.0003848431024274696</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,217 +2826,217 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.008703374777975115 +/- 0.0010524800967810176</t>
+          <t>8.880994671399689e-05 +/- 0.001503953321004209</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.012670219064535203 +/- 0.0030815899774240475</t>
+          <t>-0.01785079928952047 +/- 0.0021634738177138454</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.0006512729425695807 +/- 0.0007347349701593087</t>
+          <t>-0.0002960331557134599 +/- 0.0005616834209890379</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0002664298401421128 +/- 0.0006808762581409104</t>
+          <t>-0.0017465956187093234 +/- 0.0012729425695677875</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.001568975725281274 +/- 0.0004595670425180519</t>
+          <t>-0.0001184132622853995 +/- 0.0014634940312976189</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.011634103019538166 +/- 0.0019638849367225792</t>
+          <t>-0.011426879810538793 +/- 0.0017523562565954628</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.001361752516281811 +/- 0.0005328596802842009</t>
+          <t>0.0006808762581408722 +/- 0.00044008492443216557</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.004085257548845478 +/- 0.0008456398376012935</t>
+          <t>0.0019834221432800335 +/- 0.0015723234724558425</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.001983422143280045 +/- 0.0008378313616391447</t>
+          <t>-0.008792184724689178 +/- 0.0011469135954890728</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.00458851391355829 +/- 0.0015566390556701962</t>
+          <t>0.0014209591474244943 +/- 0.0010820406679986586</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.00011841326228534399 +/- 0.001132689548236194</t>
+          <t>0.001006512729425657 +/- 0.0011480591728635597</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.001420959147424472 +/- 0.0008761781282977429</t>
+          <t>-0.0004440497335701954 +/- 0.0009929253896535511</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.000947306098282974 +/- 0.0008352123137753462</t>
+          <t>-0.005121373593842527 +/- 0.001115931132325098</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0004144464179988261 +/- 0.001101307000458178</t>
+          <t>-0.002338661930136188 +/- 0.0008625697030392956</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0005624629958555394 +/- 0.0005986900063989708</t>
+          <t>-0.0001480165778567355 +/- 0.0003309751298845109</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0013617525162818 +/- 0.0008074707931903993</t>
+          <t>0.002279455298993449 +/- 0.0009551371110066143</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.00648312611012436 +/- 0.0020053924872042673</t>
+          <t>0.009650680876258111 +/- 0.0010771702426678703</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.002397868561278882 +/- 0.0016130411753493485</t>
+          <t>-2.9603315571358203e-05 +/- 0.0013594982241805793</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.0030787448194197543 +/- 0.0016704246275507293</t>
+          <t>-0.0021314387211368024 +/- 0.0008139566065641109</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.0010361160449970375 +/- 0.0007747929146419428</t>
+          <t>-0.0003552397868561652 +/- 0.0005262400483905141</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0011545293072824036 +/- 0.0005032563647128407</t>
+          <t>-0.0026939017169923416 +/- 0.000627283010669545</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>8.88099467140746e-05 +/- 0.0004782561995678984</t>
+          <t>-0.00112492599171109 +/- 0.0006321538337496438</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.007933688573120146 +/- 0.0015198931501472393</t>
+          <t>0.0024274718768501845 +/- 0.0013092566244816935</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.005239786856127892 +/- 0.001356917304483801</t>
+          <t>0.0066015393724096925 +/- 0.001162095111094754</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.00014801657785672439 +/- 0.0001985850779307056</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-5.9206631142683094e-05 +/- 0.000526240048390503</t>
+          <t>0.0008880994671402797 +/- 0.00035027115352869175</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.0018650088809947008 +/- 0.0010173380862900832</t>
+          <t>0.000621669626998178 +/- 0.001482827683406545</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.001657785671995282 +/- 0.0009746641582684783</t>
+          <t>0.0010953226761396873 +/- 0.0006356101407218424</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0018946121965659924 +/- 0.001018629398110436</t>
+          <t>-0.0012433392539964784 +/- 0.0005890985418038116</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.0015985790408525546 +/- 0.0011171084821855056</t>
+          <t>-0.006423919478981688 +/- 0.0008378313616391352</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.0060390763765541975 +/- 0.001654610848132869</t>
+          <t>-0.005032563647128496 +/- 0.001616026532144025</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0008979130188338048</t>
+          <t>0.0015689757252812186 +/- 0.0011845026064974916</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.006335109532267602 +/- 0.0013578857242368008</t>
+          <t>0.005091770278271157 +/- 0.0017453407901697627</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.0003848431024274679 +/- 0.00026642984014207705</t>
+          <t>8.880994671399689e-05 +/- 0.0002975096394647877</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0005624629958555727 +/- 0.0010628373635888893</t>
+          <t>-0.0071047957371225936 +/- 0.0010339993603654819</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.0010657193605684069 +/- 0.0007275432639102714</t>
+          <t>-0.005387803433984617 +/- 0.0013553017338377301</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.000976909413854332 +/- 0.000496241995685028</t>
+          <t>-0.001983422143280078 +/- 0.0005778336677307188</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.008940201302545903 +/- 0.0018853384639538797</t>
+          <t>-0.0009177027827117045 +/- 0.0010872923429370526</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.006394316163410308 +/- 0.0011171084821855152</t>
+          <t>0.001302545885139117 +/- 0.0009286197241775093</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.0008584961515689993 +/- 0.0016769696907363706</t>
+          <t>-0.0023090586145648627 +/- 0.0008959589076626358</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>2.96033155713471e-05 +/- 0.00015941873318931526</t>
+          <t>-3.3306690738754695e-17 +/- 0.00026478010390760333</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.00287152161042038 +/- 0.001100112739849721</t>
+          <t>-0.004795737122557753 +/- 0.0013159331421487884</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.0005624629958555283 +/- 0.0007424473773821552</t>
+          <t>-0.0013025458851391725 +/- 0.0008701562141325594</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0006808762581409055 +/- 0.0004400849244321663</t>
+          <t>-0.0005920663114269087 +/- 0.0006485761486147637</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-0.004026050917702739 +/- 0.0013707326113428242</t>
+          <t>0.0003256364712847515 +/- 0.0013465441581461519</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0007696862048549802 +/- 0.0004624185716937053</t>
+          <t>0.0012137359384250868 +/- 0.0003613545179317212</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.004736530491415059 +/- 0.0010169072846251067</t>
+          <t>-0.001568975725281263 +/- 0.0009733145188143003</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0031675547661337957 +/- 0.0009081031172396485</t>
+          <t>0.003818827708703365 +/- 0.0010207779543852495</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.000769686204854969 +/- 0.0008074707931904156</t>
+          <t>5.9206631142660895e-05 +/- 0.0005890985418037992</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.00127294256956777 +/- 0.001139246974830908</t>
+          <t>-0.003670811130846685 +/- 0.0010099894676869154</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.002486678507992912 +/- 0.0015048271198506659</t>
+          <t>-0.0009473060982830295 +/- 0.0009977678831470137</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0011249259917110565 +/- 0.0009619938904246088</t>
+          <t>-0.0026346950858496367 +/- 0.0009769094138543592</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.004387339392040124 +/- 0.0007415957108241449</t>
+          <t>0.00025070510811656674 +/- 0.0012039719656721068</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.002256345973049201 +/- 0.0012039719656721105</t>
+          <t>-0.0043246631150109845 +/- 0.000697933483275469</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.003196490128486351 +/- 0.0014551158591342914</t>
+          <t>-0.004732058915700421 +/- 0.0013905802401964116</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.00012535255405830004 +/- 0.0010125662438986746</t>
+          <t>0.004732058915700388 +/- 0.0014046339599507827</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0017549357568160673 +/- 0.0012313934631393375</t>
+          <t>-0.003885929175806968 +/- 0.0013745980695368993</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0069884048887496105 +/- 0.0014568021684950847</t>
+          <t>-0.0018176120338452173 +/- 0.001475224355492316</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.000313381385145739 +/- 0.000396399581343585</t>
+          <t>-0.00012535255405828893 +/- 0.0002872187837640704</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.003290504544030104 +/- 0.0015045570522291207</t>
+          <t>0.0030711375744280735 +/- 0.0009890149694803784</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.0007521153243497447 +/- 0.0025428345691132365</t>
+          <t>0.0040739580068943956 +/- 0.0022247871324724347</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0003760576621748446 +/- 0.0023401008715254793</t>
+          <t>0.01513632090253838 +/- 0.0032719477941301656</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.006142275148856147 +/- 0.0011573917463252547</t>
+          <t>0.001065496709495428 +/- 0.0017848988863551464</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0021936696960200954 +/- 0.0012535255405828922</t>
+          <t>0.0021309934189908896 +/- 0.0010562393949453174</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0001566906925728473 +/- 0.00138916704853032</t>
+          <t>0.0008147916013788615 +/- 0.0011053081848040232</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.006988404888749644 +/- 0.0017394784188502444</t>
+          <t>-0.008837355061109409 +/- 0.0019459949478232625</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.0026950799122532065 +/- 0.0009317498431412311</t>
+          <t>0.0033218426825446625 +/- 0.0016235454524586293</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.006831714196176763 +/- 0.001335460717810261</t>
+          <t>0.0012221874020683088 +/- 0.0011595111250391715</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.0005327483547477474 +/- 0.0011216252064038372</t>
+          <t>-0.005045440300846149 +/- 0.0006640432497780378</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0015042306486994673 +/- 0.001578148331183211</t>
+          <t>-0.0019743027264180644 +/- 0.0009301674760047635</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0029144468818552262 +/- 0.0011813272845484573</t>
+          <t>-0.0007207771858351753 +/- 0.001322528852774013</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.133813851456946e-05 +/- 0.00032717977151079994</t>
+          <t>0.0002820432466311473 +/- 0.0004308281756461104</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.006549670949545616 +/- 0.001159511125039167</t>
+          <t>0.0028831087433406457 +/- 0.0008951962931423228</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.00582889376371043 +/- 0.0013162018176120372</t>
+          <t>0.0026950799122531953 +/- 0.0007701789863644267</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.0030711375744281065 +/- 0.0011792471151505376</t>
+          <t>0.0015042306486994562 +/- 0.0008729795222302594</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0011281729865245782 +/- 0.0006452917669061174</t>
+          <t>0.0014728925101848867 +/- 0.0007153063121600392</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0009714822939517643 +/- 0.0006640432497780389</t>
+          <t>-0.0010654967094954615 +/- 0.0011229378168078178</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.00025070510811657786 +/- 0.0003654623563049389</t>
+          <t>0.001347539956126609 +/- 0.0005253229274284034</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.0015042306486994894 +/- 0.001008679219017937</t>
+          <t>0.0016609213412723145 +/- 0.0010677984981134934</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.003635224067690379 +/- 0.001444276856383938</t>
+          <t>-0.003102475712942665 +/- 0.0008802614794853185</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.004356001253525555 +/- 0.001404633959950803</t>
+          <t>-0.0001566906925728695 +/- 0.0008438052032489074</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.000783453462864292 +/- 0.0016056018122782433</t>
+          <t>0.003196490128486373 +/- 0.001092798230909603</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.267627702912781e-05 +/- 0.0005014102162331404</t>
+          <t>0.00028204324663112513 +/- 0.0005508742034235914</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9.401441554369727e-05 +/- 0.0005786958731626484</t>
+          <t>0.0 +/- 0.0003133813851456946</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0017549357568160673 +/- 0.0010873927654589462</t>
+          <t>0.0023190222500783287 +/- 0.0012153381027681278</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.004888749608273291 +/- 0.0013383990287723511</t>
+          <t>-0.0030711375744280956 +/- 0.0010837741438916074</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.0011281729865246226 +/- 0.0005091844816443778</t>
+          <t>-0.0003447195236603084 +/- 0.00026031412920460273</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00018802883108741674 +/- 0.000730924712609875</t>
+          <t>-0.0007834534628643252 +/- 0.0004025456778021026</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0012535255405828893 +/- 0.0007146195080533613</t>
+          <t>-0.0010654967094954615 +/- 0.0008662033820799373</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.007865872767157667 +/- 0.0017190333001444703</t>
+          <t>-0.0009401441554371948 +/- 0.0007547223176930461</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.00043873393920403905 +/- 0.0010317817382108584</t>
+          <t>0.0002193669696019862 +/- 0.0003976364005155059</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.004105296145408976 +/- 0.0010896483015176263</t>
+          <t>0.0006581009088060142 +/- 0.0013105937741351545</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.004230648699467277 +/- 0.0011320834765395553</t>
+          <t>-0.0005327483547477252 +/- 0.0010013503797349174</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0001566906925728584 +/- 0.00092168230459745</t>
+          <t>0.0015042306486994562 +/- 0.0016271707910682645</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.000846129739893442 +/- 0.001139002309331635</t>
+          <t>-0.002444374804136651 +/- 0.0009380526196863413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.0014102162331557587 +/- 0.0015432243500150664</t>
+          <t>-0.00012535255405830004 +/- 0.0007701789863644231</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.0036665622062049706 +/- 0.0009301674760047575</t>
+          <t>0.0007521153243497225 +/- 0.0010125662438986945</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0036038859291757986 +/- 0.00196332875057061</t>
+          <t>-0.00134753995612662 +/- 0.0010207770275714434</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.000908806016922592 +/- 0.00029564340746026816</t>
+          <t>-0.00018802883108745005 +/- 0.0004013239885573802</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.006424318395487305 +/- 0.0010033099713934262</t>
+          <t>-0.0020996552804763424 +/- 0.0010492428105787065</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.001096834848010031 +/- 0.0008891420218809938</t>
+          <t>0.0004700720777185641 +/- 0.0011746577758690764</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.005045440300846138 +/- 0.0011424460127582802</t>
+          <t>-0.001817612033845184 +/- 0.0010654967094954491</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.006925728611720461 +/- 0.001741735284436253</t>
+          <t>-0.004888749608273279 +/- 0.0015172320196690887</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.00031338138514572786 +/- 0.0007007420800688804</t>
+          <t>0.00040739580068941403 +/- 0.0003149443942689</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0004073958006894474 +/- 0.00042161153391018637</t>
+          <t>0.0002193669696019862 +/- 0.000864501048206442</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.0018489501723597868 +/- 0.0007983540710032522</t>
+          <t>0.0004387339392040057 +/- 0.00042509119292543366</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.006675023503603894 +/- 0.0014157764961549952</t>
+          <t>-0.005515512378564735 +/- 0.0014911159201968407</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.0015355687872140589 +/- 0.001192909201546507</t>
+          <t>-0.002507051081165801 +/- 0.0010202958693888895</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.00031338138514572786 +/- 0.0005778467224877994</t>
+          <t>0.0004387339392039946 +/- 0.0003760576621748631</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.00470072077718583 +/- 0.001221785565002702</t>
+          <t>-0.0008461297398934753 +/- 0.000908806016922605</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.003165151989971826 +/- 0.0009653977938420248</t>
+          <t>-0.0007521153243497336 +/- 0.0012550914694140136</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0004700720777185641 +/- 0.00047007207771857884</t>
+          <t>0.0006581009088060142 +/- 0.0003825307306717085</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0021309934189909117 +/- 0.0013573430164655301</t>
+          <t>-0.00034471952366029737 +/- 0.0013402322018390951</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0008774678784080447 +/- 0.001732406764159853</t>
+          <t>-0.005296145408962704 +/- 0.0010714710747275937</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0022250078345346425 +/- 0.0012092623868113217</t>
+          <t>-0.0016609213412723477 +/- 0.0008869302223807425</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.00128486367909747 +/- 0.0011679501819858466</t>
+          <t>-0.0018176120338452063 +/- 0.0006236210824861202</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.0001566906925728695 +/- 0.0003773611588465185</t>
+          <t>6.267627702912781e-05 +/- 0.0003914132245940556</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.005139454716389847 +/- 0.001105308184804025</t>
+          <t>-0.0005954246317768974 +/- 0.0008690331948519208</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0009714822939517753 +/- 0.000834442303710082</t>
+          <t>-0.001347539956126631 +/- 0.0007289065089071122</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.002851770604826076 +/- 0.0007859565154487055</t>
+          <t>-0.000313381385145739 +/- 0.000840890496082666</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.0002507051081166112 +/- 0.0015656528983762664</t>
+          <t>-0.0029457850203698068 +/- 0.0008662033820798997</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0029457850203697734 +/- 0.001293623781921037</t>
+          <t>0.00040739580068942515 +/- 0.0008757874404564197</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.011595111250391744 +/- 0.0010393684708102213</t>
+          <t>-0.006737699780633033 +/- 0.0010322575425885745</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>6.267627702913892e-05 +/- 0.0003914132245940805</t>
+          <t>0.00018802883108741674 +/- 0.00020787369416202484</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.0020369790034471926 +/- 0.0006610787561807781</t>
+          <t>0.0006894390473205725 +/- 0.0006837174625280991</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.002130993418990923 +/- 0.000968951728846155</t>
+          <t>0.00025070510811657786 +/- 0.0004387339392040073</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-6.267627702915002e-05 +/- 0.0005744375675281553</t>
+          <t>-0.000626762770291478 +/- 0.000863932858169256</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0048260733312441295 +/- 0.0010691771926814226</t>
+          <t>0.0011281729865245892 +/- 0.001031781738210864</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0006581009088060252 +/- 0.00047423208870014775</t>
+          <t>-0.0005014102162331779 +/- 0.00025070510811660285</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.002005640864932645 +/- 0.001199067782495074</t>
+          <t>9.401441554369727e-05 +/- 0.0011561182541959807</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.00363522406769039 +/- 0.0012072303531343318</t>
+          <t>0.00012535255405827784 +/- 0.0008314947766481788</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0009088060169226031 +/- 0.0005139836874602416</t>
+          <t>-0.0004073958006894585 +/- 0.0005062831219493421</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.0008461297398934309 +/- 0.001529159874491493</t>
+          <t>-0.0015042306486994894 +/- 0.0007777921432774114</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.005264807270448158 +/- 0.0010746742838910724</t>
+          <t>-0.001159511125039181 +/- 0.0008177993325415244</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.004888749608273268 +/- 0.000962851237589314</t>
+          <t>0.001378878094641156 +/- 0.0009929789732218627</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.005117004680187253 +/- 0.0010081431776226798</t>
+          <t>0.005335413416536627 +/- 0.0016943742879732167</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0004992199687987031 +/- 0.001064506839889656</t>
+          <t>0.0015912636505459599 +/- 0.003048954285473136</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.003962558502340152 +/- 0.00116786067221296</t>
+          <t>-0.0010608424336973955 +/- 0.0016813970153269798</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0023400936037440644 +/- 0.0018153121008160724</t>
+          <t>0.0039937597503899806 +/- 0.00206400441916274</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.0006552262090484207 +/- 0.0019357350850853158</t>
+          <t>0.018252730109204317 +/- 0.0018524714644364852</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0013416536661465805 +/- 0.0019883299802002977</t>
+          <t>0.00851794071762868 +/- 0.0021664094024137206</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0006864274570982154 +/- 0.00033604772587421606</t>
+          <t>0.00021840873634941803 +/- 0.00041976986106315574</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.001528861154446115 +/- 0.0016418498741869471</t>
+          <t>0.019001560062402455 +/- 0.002221432450711715</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.004586583463338467 +/- 0.0027663738094624453</t>
+          <t>0.014976599063962547 +/- 0.002926936511590286</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.02287051482059279 +/- 0.004787231392995825</t>
+          <t>0.020780031201248005 +/- 0.004032572710490727</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.008923556942277745 +/- 0.001831064056302178</t>
+          <t>0.010109204368174673 +/- 0.001909149271860013</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0009360374414976059 +/- 0.0014634682557951543</t>
+          <t>-0.012074882995319858 +/- 0.0014966845497923619</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.004492979719188828 +/- 0.0015675328158602604</t>
+          <t>0.01781591263650544 +/- 0.003315123428453849</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.016380655226208997 +/- 0.0024498444296353933</t>
+          <t>0.021528861154446143 +/- 0.0031201248049922015</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.005491419656786234 +/- 0.001610419706778651</t>
+          <t>0.014758190327613075 +/- 0.002584435368471619</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.0015600624024960541 +/- 0.0016272580106590122</t>
+          <t>0.006521060842433646 +/- 0.002298962498569557</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0035881435257410833 +/- 0.0013182296520609957</t>
+          <t>-0.003525741029641227 +/- 0.0015728028906244664</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0009672386895475338 +/- 0.0008764163435374636</t>
+          <t>-0.0023712948517941148 +/- 0.0018416667161776847</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.005647425897035929 +/- 0.0010848885273456272</t>
+          <t>0.0018408736349453613 +/- 0.0015440677730619167</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-6.240249609986703e-05 +/- 0.00041393133108959127</t>
+          <t>0.0004056162246489414 +/- 0.0005761680284748617</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00421216848673941 +/- 0.0012958851580215374</t>
+          <t>0.005335413416536617 +/- 0.0015440677730619325</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.007488299531981313 +/- 0.001933470625251755</t>
+          <t>-0.004617784711388506 +/- 0.001206806839676367</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0031513260530420693 +/- 0.0008652371060132253</t>
+          <t>0.006115444617784671 +/- 0.0009787449074170587</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.005210608424336927 +/- 0.0014704364016159955</t>
+          <t>0.006677067082683253 +/- 0.0013542923191395117</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.003276131045241759 +/- 0.001152758390134877</t>
+          <t>0.010920436817472656 +/- 0.0014298208096586032</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0009360374414975947 +/- 0.0005404214688202305</t>
+          <t>0.0007176287051481655 +/- 0.0008021815995121619</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.005366614664586522 +/- 0.0017135139117311529</t>
+          <t>0.00945397815912632 +/- 0.0021574032964820646</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0012792511700468467 +/- 0.0017397319013354963</t>
+          <t>-0.01145085803432142 +/- 0.0023183598113272973</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.0071762870514821 +/- 0.0017814792416374569</t>
+          <t>-0.0017784711388455833 +/- 0.0015789804591426007</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.00443057722308896 +/- 0.0013585985059018598</t>
+          <t>-0.0033697347893916207 +/- 0.0012925001670644697</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0014352574102964755 +/- 0.0005952818729590923</t>
+          <t>-0.0012792511700468578 +/- 0.0005484678886504716</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.00031201248049924637 +/- 0.0005581448929796556</t>
+          <t>0.0004368174726988805 +/- 0.0005952818729590899</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.005553822152886157 +/- 0.0009945321341971514</t>
+          <t>-0.006614664586583519 +/- 0.0012148469475152534</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.0044617784711389 +/- 0.0012792511700467964</t>
+          <t>-0.003993759750390069 +/- 0.0013296271920538254</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0005304212168487199 +/- 0.0012406174946690241</t>
+          <t>0.0020280811232448737 +/- 0.0011097297500017903</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0006552262090482985 +/- 0.000472160560075541</t>
+          <t>-0.0006864274570983153 +/- 0.0005887039707991637</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.0021216848673947463 +/- 0.0015208808245808472</t>
+          <t>0.011575663026521032 +/- 0.002004907809849279</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.0040873634945398415 +/- 0.0014664586583463296</t>
+          <t>-0.004180967238689592 +/- 0.001793461199775334</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0009360374414977057 +/- 0.0005581448929796803</t>
+          <t>0.00124804992199683 +/- 0.000936037441497654</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0030889235569422245 +/- 0.0016886189238982593</t>
+          <t>-0.0001872074882995678 +/- 0.0018834805956676015</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.007675507020280858 +/- 0.0015234390784066817</t>
+          <t>-0.005366614664586611 +/- 0.0010042731319457865</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0027457098283930836 +/- 0.0017583778850053335</t>
+          <t>0.00730109204368169 +/- 0.0014846024653192313</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.007176287051482122 +/- 0.0016975314207469993</t>
+          <t>0.003993759750389969 +/- 0.001661594627855754</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.004648985959438445 +/- 0.0012120389765712903</t>
+          <t>-0.00031201248049925743 +/- 0.0025386390772927096</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.0009984399375975617 +/- 0.0007868655359075397</t>
+          <t>0.006302652106084194 +/- 0.00128494603943676</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0007488299531980824 +/- 0.0010915978586293683</t>
+          <t>0.007113884555382177 +/- 0.0024639110168361406</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.00037441497659900235 +/- 0.0004585628223618753</t>
+          <t>0.0006240249609983928 +/- 0.0004186086697347308</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.00742589703588149 +/- 0.0010790400290664878</t>
+          <t>0.004430577223088883 +/- 0.0015144662838704036</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.0045865834633386 +/- 0.0010722521233971518</t>
+          <t>0.00421216848673942 +/- 0.00180994134318543</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.016411856474259023 +/- 0.0013897695757454044</t>
+          <t>0.002995319812792463 +/- 0.0008039999205444839</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.00861154446177852 +/- 0.0013325526679602245</t>
+          <t>-0.016723868954758237 +/- 0.001998829001940315</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0003432137285491077 +/- 0.000492347389643023</t>
+          <t>-6.240249609987814e-05 +/- 0.0006662763339801136</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.001591263650545971 +/- 0.000646250083532237</t>
+          <t>-0.0008736349453978609 +/- 0.00043681747269890274</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.00124804992199693 +/- 0.00031201248049923526</t>
+          <t>-0.0016848673946958325 +/- 0.00020696566554478813</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.010608424336973543 +/- 0.0009566121508116057</t>
+          <t>-0.0013104524180967748 +/- 0.001828936148487099</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.0007800312012480881 +/- 0.0016642290612286325</t>
+          <t>0.007394695787831451 +/- 0.0022327975866227438</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,107 +3841,107 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0003432137285490855 +/- 0.0003543780559001539</t>
+          <t>0.0032761310452417702 +/- 0.00046801872074883806</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0027457098283931946 +/- 0.000857892485795162</t>
+          <t>0.0032449297971918313 +/- 0.0010272747352982644</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.006333853354134211 +/- 0.00170924754131699</t>
+          <t>0.0029017160686427234 +/- 0.0016095126834981541</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.002340093603744109 +/- 0.0009692495829647054</t>
+          <t>0.0005616224648985702 +/- 0.0006208969966343789</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0019968798751950566 +/- 0.0009586453351474291</t>
+          <t>-0.002496099843993793 +/- 0.0011506451740771098</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.0040873634945398415 +/- 0.0016653985828496178</t>
+          <t>0.0030577223088923077 +/- 0.0017360908259898393</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.0016536661466459157 +/- 0.0020604638977970904</t>
+          <t>-0.003307332293291754 +/- 0.0017157849715903211</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.0013104524180966638 +/- 0.0008112324492979588</t>
+          <t>0.004461778471138799 +/- 0.0013387480781856362</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.00031201248049916863 +/- 0.0</t>
+          <t>0.000280811232449274 +/- 0.00035437805590017536</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.00421216848673941 +/- 0.0018629522918599812</t>
+          <t>0.010826833073322894 +/- 0.001248439876676611</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0011856474258970739 +/- 0.00150155499725629</t>
+          <t>-0.0020280811232449626 +/- 0.0014040561622464896</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0028081123244929284 +/- 0.0011249769970246577</t>
+          <t>0.001560062402496043 +/- 0.0006691922180819659</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.008954758190327561 +/- 0.0019286813679283284</t>
+          <t>0.0109828393135725 +/- 0.002068715688518031</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0013416536661467026 +/- 0.0010539373325463303</t>
+          <t>-0.005429017160686467 +/- 0.0007004662814553454</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0008736349453977388 +/- 0.002253412803153551</t>
+          <t>0.009235569422776858 +/- 0.0013614617303757464</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>6.240249609981152e-05 +/- 0.00023348876048511052</t>
+          <t>-0.0003432137285491632 +/- 0.00032575059310172537</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6.240249609980042e-05 +/- 0.0006662763339801001</t>
+          <t>-0.00012480499219972297 +/- 0.00048737907493959215</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0011856474258969741 +/- 0.00045856282236190853</t>
+          <t>0.0034945397815912215 +/- 0.000774394611294272</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>0.00015600624024958432 +/- 0.00015600624024958432</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.00043681747269883606 +/- 0.00046697752097021666</t>
+          <t>0.0007176287051481767 +/- 0.000725722517916552</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.003276131045241859 +/- 0.0014584706262115712</t>
+          <t>0.0007176287051481655 +/- 0.0016630587171589898</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0016848673946957104 +/- 0.0006114170964825351</t>
+          <t>-0.000436817472698936 +/- 0.000399570935253227</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0013104524180966748 +/- 0.001922361535194922</t>
+          <t>-0.0007800312012480992 +/- 0.0007924134227269994</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.002964118564742535 +/- 0.0016758875509510997</t>
+          <t>0.007581903276130997 +/- 0.001877527161726116</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-6.240249609985593e-05 +/- 0.0006363830906199954</t>
+          <t>0.002028081123244885 +/- 0.000862983880557835</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>9.360374414971729e-05 +/- 0.001395711029413113</t>
+          <t>-0.0023400936037441976 +/- 0.000862983880557825</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.003026521060842369 +/- 0.0018566708950779225</t>
+          <t>0.010858034321372811 +/- 0.0009846947792860996</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0019968798751949456 +/- 0.0011438566477268966</t>
+          <t>-0.0027457098283931837 +/- 0.0012620123816634472</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0016209843796050395 +/- 0.001252145345490601</t>
+          <t>0.0025051576775715124 +/- 0.0012311581829770317</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.011140583554376637 +/- 0.0019182010132947713</t>
+          <t>0.003949307397583313 +/- 0.002138326807806305</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0156498673740053 +/- 0.0016902388398396231</t>
+          <t>0.01470674918950785 +/- 0.0010332182813414597</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0028588269967580017 +/- 0.0016778597497778152</t>
+          <t>0.004302976716769868 +/- 0.0012724452192704443</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.010875331564986723 +/- 0.001385204833480694</t>
+          <t>0.0024462127910404143 +/- 0.0006727210262607424</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.005216622458001763 +/- 0.0015819318479598893</t>
+          <t>0.001915708812260586 +/- 0.0013262599469496064</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.89448865311204e-05 +/- 0.0004126142057176525</t>
+          <t>0.00017683465959332788 +/- 0.00014438489494747052</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.007810197465369861 +/- 0.0018790849548240608</t>
+          <t>0.005865016209843843 +/- 0.0019525354641971098</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04061302681992336 +/- 0.0020748265142113654</t>
+          <t>0.040996168582375536 +/- 0.0023850837614129354</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.04665487768936044 +/- 0.0017488362745825858</t>
+          <t>0.047686413203654646 +/- 0.0032998608906049938</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2.9472443265532446e-05 +/- 0.0017557761283355686</t>
+          <t>-0.0022399056881815095 +/- 0.0015097257264798988</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.010521662245800178 +/- 0.0012984609945128668</t>
+          <t>0.007338638373121176 +/- 0.0013340961152674433</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.012967875036840548 +/- 0.001787886930516126</t>
+          <t>0.014176245210728012 +/- 0.0020138544421876127</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.00011788977306216308 +/- 0.0030944661947319013</t>
+          <t>-0.00041261420571760967 +/- 0.0023732180535452375</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.017447686413203635 +/- 0.0025955837142710336</t>
+          <t>0.02758620689655178 +/- 0.002347457441997035</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.006867079280872368 +/- 0.0010548499951767395</t>
+          <t>0.004597701149425348 +/- 0.0023326093648581786</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.009048040082522824 +/- 0.0009040885145993494</t>
+          <t>0.0020041261420572277 +/- 0.0016609493431895715</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.002770409666961382 +/- 0.001306131435671089</t>
+          <t>-0.0031240789861479044 +/- 0.0014269046197359614</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.008635425876805181 +/- 0.0020207438510370847</t>
+          <t>0.004244031830238781 +/- 0.0012517984427701358</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00014736221632771773 +/- 0.00019770715981428375</t>
+          <t>0.000176834659593339 +/- 0.0003536693191865669</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.006336575302092562 +/- 0.0025836761501848715</t>
+          <t>-0.009254347185381618 +/- 0.0018695846185857496</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.0041850869437076495 +/- 0.0017022728061530832</t>
+          <t>-0.002475685234305869 +/- 0.0015039611933006824</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0028882994400235783 +/- 0.0008919979929514455</t>
+          <t>0.0016799292661362152 +/- 0.0012226624528553737</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.005334512231063937 +/- 0.0014644572058714787</t>
+          <t>-0.003448275862068917 +/- 0.0008846643689834075</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.004214559386973182 +/- 0.0008944291721481532</t>
+          <t>0.0017094017094017588 +/- 0.0010106942646320141</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0012673150604184946 +/- 0.0010128405704355685</t>
+          <t>0.0005010315355143402 +/- 0.0005280422300963587</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.008635425876805169 +/- 0.0014441497200117775</t>
+          <t>0.005010315355143002 +/- 0.0023467172693656707</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.0053345122310639705 +/- 0.001956979110054111</t>
+          <t>-0.010344827586206851 +/- 0.002073360723484998</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.006424992631889215 +/- 0.0023533704424022455</t>
+          <t>-0.0023872679045092494 +/- 0.001842675983771362</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0005010315355142847 +/- 0.0013314891833865674</t>
+          <t>-0.0007368110816386219 +/- 0.0014868256122168373</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0009136457412319387 +/- 0.0008688124357785854</t>
+          <t>-2.9472443265488034e-05 +/- 0.0005345817019515729</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0008547008547008406 +/- 0.0007273187550399835</t>
+          <t>-0.0009136457412318944 +/- 0.0005661471474299663</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.00185676392572941 +/- 0.0020034759091491126</t>
+          <t>-0.0025346301208369892 +/- 0.0020385047410304193</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0022693781314471195 +/- 0.0021619599098253186</t>
+          <t>-0.012466843501326198 +/- 0.0020164407289239403</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0002652519893899141 +/- 0.0006245098762280434</t>
+          <t>5.89448865311315e-05 +/- 0.0003681106984025058</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.003271441202475711 +/- 0.000426078169608042</t>
+          <t>-0.00017683465959321686 +/- 0.0006068747504265858</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.001797819039198323 +/- 0.0010581387015040698</t>
+          <t>-0.0036545829649277327 +/- 0.0015550729099054461</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.004568228706159772 +/- 0.0012863632680692723</t>
+          <t>-0.0029177718832890777 +/- 0.0013210100106698947</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0009136457412319277 +/- 0.0006382672510376518</t>
+          <t>0.00038314176245215494 +/- 0.000844476792330941</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.00041261420571764296 +/- 0.001047827222789949</t>
+          <t>0.0031830238726790806 +/- 0.0021968340882504217</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.005923961096374908 +/- 0.0011218901450441685</t>
+          <t>0.0009725906277630924 +/- 0.0017035480125692113</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0030946065428823833 +/- 0.0011433636746991378</t>
+          <t>0.0016799292661362041 +/- 0.0007104020508808714</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.004008252284114377 +/- 0.0013898999260302427</t>
+          <t>-0.013822575891541367 +/- 0.001720797002887721</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.006837606837606813 +/- 0.0021849399343177862</t>
+          <t>0.01797819039198355 +/- 0.0022133785270284276</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0020925434718538248 +/- 0.001066316092845592</t>
+          <t>0.0023577954612437725 +/- 0.0010948526743888441</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.00029472443265543546 +/- 0.0016356542205141892</t>
+          <t>0.010639552018862419 +/- 0.0014762723001907699</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.00041261420571768735 +/- 0.0004966784422738731</t>
+          <t>-0.0016209843796050282 +/- 0.0007128433022368455</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.004214559386973182 +/- 0.0017137155036966475</t>
+          <t>0.007987032124963222 +/- 0.00125353199635348</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.016740347774830522 +/- 0.0016765650048131693</t>
+          <t>-0.006336575302092496 +/- 0.0015664818468515483</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.007810197465369861 +/- 0.000886625933185475</t>
+          <t>0.0020630710285883145 +/- 0.002236801174301217</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.004391394046566443 +/- 0.0016591179422384614</t>
+          <t>0.0022104332449160435 +/- 0.0012098069998098219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.0005305039787798172 +/- 0.0006154026825175641</t>
+          <t>0.0018272914824639442 +/- 0.001109041421881918</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.00035366931918654474 +/- 0.0006694852161273575</t>
+          <t>0.002740937223695894 +/- 0.0008444767923309258</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-2.9472443265554648e-05 +/- 0.0003347426080636592</t>
+          <t>-0.00014736221632771773 +/- 0.0002376144340789179</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.0006189213085764922 +/- 0.0013598905977081424</t>
+          <t>0.0004126142057177207 +/- 0.0009055285290738121</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.00963748894783376 +/- 0.0011569576437601154</t>
+          <t>0.0098143236074271 +/- 0.0017288546272988656</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>0.0012967875036840493 +/- 0.0004966784422738863</t>
+          <t>0.0005599764220454384 +/- 0.0006778661951075837</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0006483937518420135 +/- 0.0006949499630151351</t>
+          <t>0.005658709106985005 +/- 0.0011011813552767307</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.0008252284114353304 +/- 0.0009667680204454449</t>
+          <t>-0.0047745358090185205 +/- 0.0009667680204454436</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.0014146772767462457 +/- 0.0006823363927374067</t>
+          <t>0.0014441497200118226 +/- 0.00080659782984992</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.00312407898614796 +/- 0.0014806786545335118</t>
+          <t>0.0014736221632773772 +/- 0.0014438489494743064</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.005393457117595035 +/- 0.0013509185542429488</t>
+          <t>0.00445033893309762 +/- 0.001870745779258277</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.004420866489832009 +/- 0.0018310904293556295</t>
+          <t>0.002092543471853858 +/- 0.001007681756397216</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.001178897730621864 +/- 0.0013570131957820481</t>
+          <t>-0.009431181844974901 +/- 0.0011027578505080759</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.00020630710285880484 +/- 0.00018871571580996645</t>
+          <t>2.9472443265576854e-05 +/- 0.00020630710285884766</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.0028588269967580017 +/- 0.001103151622293709</t>
+          <t>0.002033598585322782 +/- 0.0022501587971266025</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.0005894488653109154 +/- 0.0008742939566278333</t>
+          <t>0.005305039787798449 +/- 0.0009036079998087662</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.0015915119363394958 +/- 0.0009150707159599271</t>
+          <t>0.0006483937518420579 +/- 0.0007195140357049007</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.001061007957559701 +/- 0.0012587183320991735</t>
+          <t>-0.0009136457412319054 +/- 0.0023298148156760175</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.004980842911877415 +/- 0.0011748382804594624</t>
+          <t>0.002239905688181587 +/- 0.0014981744800635322</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-0.006513409961685835 +/- 0.0012535319963534717</t>
+          <t>-0.005688181550250482 +/- 0.0022447478955885235</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0.0001178897730621853 +/- 0.00035366931918654664</t>
+          <t>0.00023577954612440387 +/- 0.00034370479780993114</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.00020630710285882703 +/- 0.0007461826643779612</t>
+          <t>-0.001002063071028536 +/- 0.0007708044108825262</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.0016209843796050726 +/- 0.0007485072265959396</t>
+          <t>0.0007368110816387107 +/- 0.0007485072265959549</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0013852048334807132 +/- 0.0005901852164603886</t>
+          <t>-0.0010315355142940907 +/- 0.0004975521077551983</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0015620394930739856 +/- 0.0014797984333195682</t>
+          <t>0.005452402004126178 +/- 0.0011509357023145716</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.0027114647804303282 +/- 0.0002569348036275084</t>
+          <t>-0.0025935750073680652 +/- 0.0004331546848423028</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.00017683465959330568 +/- 0.0006068747504265868</t>
+          <t>-0.0011788977306218308 +/- 0.0006974453030473914</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.003801945181255506 +/- 0.0014465536329865132</t>
+          <t>-0.0050692602416739785 +/- 0.0013811228427774893</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.0023577954612437613 +/- 0.0015980479471530732</t>
+          <t>0.0006189213085765255 +/- 0.0013405912662003085</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.005010315355142958 +/- 0.0008017371357934198</t>
+          <t>0.002122015915119413 +/- 0.0010192523705152155</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.0032124963159446017 +/- 0.0019569791100541288</t>
+          <t>0.019834954317712983 +/- 0.0018218166178043927</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.0009136457412319609 +/- 0.0011218901450441535</t>
+          <t>0.014353079870321283 +/- 0.0016570224340549077</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.000825228411435297 +/- 0.0011920865556237462</t>
+          <t>0.001827291482463933 +/- 0.0011920865556237503</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.002420051858254091 +/- 0.001276780167453787</t>
+          <t>-0.002535292422932911 +/- 0.0010764357068435264</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.007605877268798611 +/- 0.0013768715811407171</t>
+          <t>0.0018726591760299227 +/- 0.0014760804906308906</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.008210890233362123 +/- 0.001646216609295482</t>
+          <t>-0.01109190435033136 +/- 0.001850364819744335</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.0006626332469028773 +/- 0.00190691797676437</t>
+          <t>0.003630077787381136 +/- 0.0017769108550975802</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00849899164505904 +/- 0.0011965750306709951</t>
+          <t>-0.00017286084701818584 +/- 0.00129613620042661</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0002016709881878742 +/- 0.0018314278392754647</t>
+          <t>-0.009334485738980158 +/- 0.0012304325268834692</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.762028233936567e-05 +/- 0.00017286084701815252</t>
+          <t>0.00011524056467874245 +/- 0.0002304811293575265</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0031979256698358217 +/- 0.0010659752232785881</t>
+          <t>0.001959089599538999 +/- 0.0010993249224050094</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.007375396139441071 +/- 0.00277296673362511</t>
+          <t>8.643042350904295e-05 +/- 0.0027058536120849325</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.003514837222702427 +/- 0.00318166238946207</t>
+          <t>-0.002736963411120763 +/- 0.0035943465616988437</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0016709881878421596 +/- 0.0014622388407317325</t>
+          <t>-0.0014981273408239848 +/- 0.00129357213025892</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.005214635551714197 +/- 0.0010502867262205888</t>
+          <t>-0.015010083549409437 +/- 0.0020713269337964526</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.0007202535292422652 +/- 0.0014303879674222135</t>
+          <t>-0.009363295880149836 +/- 0.0025647499012914085</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.009219245174301316 +/- 0.0020574556117956967</t>
+          <t>-0.005473926822241448 +/- 0.002406983413910163</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.01284932296168254 +/- 0.0019505976237177522</t>
+          <t>0.0022183808700662277 +/- 0.0043081517964597</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0014405070584845524 +/- 0.001152405646787652</t>
+          <t>0.000777873811581642 +/- 0.0012561353705901445</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.006511091904350308 +/- 0.0008662227818134711</t>
+          <t>-0.003370786516853963 +/- 0.0013330723481716127</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0019590895995390324 +/- 0.0009000575829336306</t>
+          <t>0.0037165082108902014 +/- 0.0009507346585998263</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.005358686257562639 +/- 0.0013152073996558088</t>
+          <t>-0.009363295880149836 +/- 0.002571214309532145</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.00011524056467873133 +/- 0.00029380694402724925</t>
+          <t>-0.00011524056467879796 +/- 0.00014114029056662848</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.001987899740708743 +/- 0.0015160267492852625</t>
+          <t>-0.003860558916738721 +/- 0.0009037388154052404</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.001670988187842104 +/- 0.0010841191427384902</t>
+          <t>0.008153269951022713 +/- 0.0012758046571872477</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5.762028233941008e-05 +/- 0.0010451372599952077</t>
+          <t>0.0028810141169691495 +/- 0.0013139445982127617</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0029386343993085817 +/- 0.0010128721308698813</t>
+          <t>0.004436761740132489 +/- 0.0012100259291270596</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0019302794583693883 +/- 0.0010311455009030883</t>
+          <t>0.004840103716508193 +/- 0.0009795447997695383</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.00020167098818786312 +/- 0.00034210147182478317</t>
+          <t>-0.00037453183520603784 +/- 0.0002895383353823424</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0035724575050418038 +/- 0.0010403612840834088</t>
+          <t>-0.0007778738115816863 +/- 0.0015624024042588508</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.00031691155286658337 +/- 0.001493966253237012</t>
+          <t>0.0022471910112359496 +/- 0.0018662212320024814</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.003428406799193351 +/- 0.0009241725688473347</t>
+          <t>-0.0031691155286661223 +/- 0.0014231159936881033</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.011322385479688824 +/- 0.001893814857913536</t>
+          <t>0.0067703831748775365 +/- 0.0024623823892643685</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0004321521175454035 +/- 0.0003700729639488616</t>
+          <t>0.0010083549409391824 +/- 0.00043215211754538504</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0013828867761452313 +/- 0.0006416323091708539</t>
+          <t>0.000777873811581642 +/- 0.0004998372680177985</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.010314030538749607 +/- 0.0013377339978385293</t>
+          <t>0.006338231057332144 +/- 0.0020208214251512596</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.00386055891673871 +/- 0.0011681437587273567</t>
+          <t>-0.0010659752232786146 +/- 0.0013268313384810593</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.0012388360702967338 +/- 0.00042829353924860145</t>
+          <t>0.0008643042350907181 +/- 0.0005466339948432875</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.00014405070584843082 +/- 0.0007316868394814347</t>
+          <t>0.00034572169403629394 +/- 0.0009183161884476783</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.0018150388936906126 +/- 0.0010550177714549378</t>
+          <t>0.0043503313166234235 +/- 0.0014257381770853958</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.0045808124459810196 +/- 0.0012913243924525797</t>
+          <t>0.002794583693460062 +/- 0.0015624024042588634</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0009219245174301061 +/- 0.00028228058113318903</t>
+          <t>-8.643042350912067e-05 +/- 0.0008453702535938488</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.004091040046096261 +/- 0.0015450403546864628</t>
+          <t>0.0006914433880725656 +/- 0.0010947853644482884</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0070584845865744985 +/- 0.0013589716410337853</t>
+          <t>0.005445116681071704 +/- 0.0013783778408419146</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0030250648228176023 +/- 0.0011896181401361435</t>
+          <t>-0.003370786516853963 +/- 0.0010230642987360675</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.0024776721405934564 +/- 0.0010947853644482763</t>
+          <t>-0.026073177758571053 +/- 0.0013155229106114475</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.0024488619994238125 +/- 0.0015312800075964557</t>
+          <t>0.004811293575338482 +/- 0.0023193505690093583</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0018150388936905904 +/- 0.0013879791956722472</t>
+          <t>-0.0004321521175454035 +/- 0.0006968243516247661</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.007058484586574454 +/- 0.0018232517813076105</t>
+          <t>-0.007605877268798644 +/- 0.0013647616574274876</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.00014405070584843082 +/- 0.0003221071704839973</t>
+          <t>-0.00014405070584849744 +/- 0.0003469200397232111</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0009795447997695494 +/- 0.0013088812090579582</t>
+          <t>0.004235090751944659 +/- 0.001181215787957369</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.0024488619994237682 +/- 0.0014928546710494398</t>
+          <t>-0.010919043503313209 +/- 0.001026304415474331</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.012129069432440177 +/- 0.0016371158334976006</t>
+          <t>-0.018582541054451184 +/- 0.0012640398137989302</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.003860558916738721 +/- 0.0018001151658672946</t>
+          <t>-0.00993949870354367 +/- 0.001430387967422235</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-0.0021319504465571516 +/- 0.0007534829634469482</t>
+          <t>-0.00011524056467879796 +/- 0.0008169084920056374</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.0008354940939210964 +/- 0.00047252144819521195</t>
+          <t>0.0017574186113511804 +/- 0.0004546163594946402</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0001288428681936019</t>
+          <t>-0.0002592912705272621 +/- 0.00032722030226449986</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.009737827715355762 +/- 0.0015124638142790545</t>
+          <t>-0.03059636992221264 +/- 0.0013126805819526958</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.007404206280610759 +/- 0.0014693171996542922</t>
+          <t>-0.01918755401901472 +/- 0.0014242820045299203</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.0005185825410544021 +/- 0.0005876138880544877</t>
+          <t>0.0010371650821088597 +/- 0.0005645611622663803</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.004119850187265917 +/- 0.0007294145146166607</t>
+          <t>0.0014116969173148751 +/- 0.0010890843083512453</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.001901469317199611 +/- 0.0012438509446800975</t>
+          <t>-0.007000864304235121 +/- 0.0016197859748626542</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0003457216940363272 +/- 0.00047863001226838945</t>
+          <t>0.0013540766349754874 +/- 0.00048294596987153354</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.005646787669259556 +/- 0.0016102781460653505</t>
+          <t>-0.0033995966580236403 +/- 0.0011068494792451017</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.020512820512820485 +/- 0.0014565513868930514</t>
+          <t>-0.011927398444252401 +/- 0.001867999432722255</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.0014405070584845524 +/- 0.0009201221217327149</t>
+          <t>0.005589167386920146 +/- 0.0024890361355753322</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.0020743301642178412 +/- 0.0012676462114664202</t>
+          <t>0.012013828867761445 +/- 0.0010783616981972263</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-8.643042350905405e-05 +/- 0.00025929127052722387</t>
+          <t>0.0005473926822240904 +/- 0.00015514735831560547</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0009795447997695383 +/- 0.0016459644894365657</t>
+          <t>0.005214635551714175 +/- 0.0013903691745334008</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0037165082108902682 +/- 0.0008781187354726844</t>
+          <t>0.004407951598962801 +/- 0.0013759670338529967</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.00028810141169688386 +/- 0.0010226585623335739</t>
+          <t>-0.000605012964563545 +/- 0.0008492885608172598</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.005934889080956507 +/- 0.0015471877363408325</t>
+          <t>0.020944972630365856 +/- 0.0017384240670176366</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.0030538749639873685 +/- 0.0014007773876281305</t>
+          <t>0.001526937481993651 +/- 0.001269282095759763</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.005531547104580847 +/- 0.002011764938069276</t>
+          <t>0.012647651973494645 +/- 0.0015803616423973083</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>2.8810141169743898e-05 +/- 0.000374531835205996</t>
+          <t>-5.762028233939898e-05 +/- 0.00011524056467879796</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-5.762028233934347e-05 +/- 0.0008719530942334592</t>
+          <t>0.0007202535292422541 +/- 0.0007757367915780006</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.0023048112935753263 +/- 0.001022658562333555</t>
+          <t>0.005877268798617085 +/- 0.0011962281470485159</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.000201670988187852 +/- 0.0007627889538965058</t>
+          <t>0.004033419763756807 +/- 0.00038652860458078086</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.00164217804667246 +/- 0.0008647842708040191</t>
+          <t>0.0075770671276289 +/- 0.0010783616981972306</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0006338231057332444 +/- 0.0005280986107698921</t>
+          <t>-0.001296456352636166 +/- 0.0010951643796455234</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.004955344281186991 +/- 0.001241178866524782</t>
+          <t>0.004609622587150653 +/- 0.0009019000773551495</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0030538749639873464 +/- 0.0012767801674537877</t>
+          <t>0.005041774704696034 +/- 0.0015149313540921716</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.002362431575914681 +/- 0.0010993249224049931</t>
+          <t>0.00025929127052718435 +/- 0.0011265465166244422</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0012388360702967117 +/- 0.0016801524992017679</t>
+          <t>0.005790838375107998 +/- 0.0016269441548251628</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.003572457505041815 +/- 0.001087177312827032</t>
+          <t>0.0053298761163929394 +/- 0.0013650657148351422</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0013540766349754985 +/- 0.0006050129645635189</t>
+          <t>-0.0010947853644482919 +/- 0.0008429120621335467</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.003093396787626401 +/- 0.0008221460417064305</t>
+          <t>-0.0021118381915526617 +/- 0.001397977394408088</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0032123735871504855 +/- 0.003009313472918922</t>
+          <t>-0.002260559190957767 +/- 0.0019422757545882728</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.007168352171326597 +/- 0.0016207177544111102</t>
+          <t>0.006870910172516365 +/- 0.0016370122434047547</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0030636525877454244 +/- 0.0014635234503441467</t>
+          <t>0.006246281975014867 +/- 0.0012263847785894352</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0010113027959547604 +/- 0.0012350112725774307</t>
+          <t>-0.0027959547888161797 +/- 0.001145827500550766</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0020820939916716187 +/- 0.0015626324255280867</t>
+          <t>0.0023497917906008304 +/- 0.0012510256302684856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.9744199881021062e-05 +/- 0.0003105385636201606</t>
+          <t>0.00032718619869124275 +/- 0.0003105385636201808</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.004669839381320639 +/- 0.0015909671767181872</t>
+          <t>0.0004759071980963703 +/- 0.0009041453987846893</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.01936347412254613 +/- 0.002207692982036104</t>
+          <t>0.03664485425342058 +/- 0.0014001906360428054</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.022665080309339704 +/- 0.003147268070532137</t>
+          <t>0.031112433075550273 +/- 0.002471454857565849</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0018441403926234723 +/- 0.0010541371294865726</t>
+          <t>-0.0014574657941701541 +/- 0.0011630704816190925</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0005948839976204323 +/- 0.0019322286459145352</t>
+          <t>0.0008030933967876352 +/- 0.0012900207282689773</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.007138607971445577 +/- 0.0014872099940511708</t>
+          <t>0.009756097560975618 +/- 0.0020120802528599308</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.019274241522903045 +/- 0.002533675126596885</t>
+          <t>0.01891731112433077 +/- 0.0016356605692882122</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.027483640690065446 +/- 0.002395100789910479</t>
+          <t>0.0252528256989887 +/- 0.002671850466424147</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.00416418798334327 +/- 0.0012118708380406522</t>
+          <t>0.0013384889946460477 +/- 0.001592078963839681</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.004015466983938098 +/- 0.001652075440451959</t>
+          <t>-0.00038667459845329597 +/- 0.0016933307944664187</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.005502676977989307 +/- 0.0025904790445928595</t>
+          <t>0.0035990481856037924 +/- 0.0012858992457595178</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.002766210588935136 +/- 0.0015685659575770596</t>
+          <t>-0.0005948839976204767 +/- 0.0006516627691911541</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0003866745984532849 +/- 0.0004001672827802942</t>
+          <t>0.0003866745984532849 +/- 0.00023230962748087164</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.004074955383700151 +/- 0.001895478163754293</t>
+          <t>-0.001070791195716836 +/- 0.0016083885585479933</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.001963117192147523 +/- 0.0010658223002479868</t>
+          <t>-0.0002379535990481907 +/- 0.0007013578895033512</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0063652587745389845 +/- 0.0013248695687876305</t>
+          <t>0.0019928613920285553 +/- 0.0006523412313938502</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0033016061867936044 +/- 0.0012439335910961564</t>
+          <t>0.0028554431885782438 +/- 0.001206016355307146</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.007674003569304 +/- 0.001611685566227735</t>
+          <t>0.008596073765615697 +/- 0.001193109525290407</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0009518143961927628 +/- 0.0006489418271645444</t>
+          <t>-0.0008030933967876242 +/- 0.0006246281975014873</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.01885782272456874 +/- 0.002035685738520962</t>
+          <t>0.016389054134443783 +/- 0.002461590878786505</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.011540749553837026 +/- 0.002738405541102654</t>
+          <t>0.008506841165972634 +/- 0.0018915066145847306</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0034205829863177216 +/- 0.0018055978834950856</t>
+          <t>-0.0009518143961927628 +/- 0.0010790218410004228</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.001070791195716858 +/- 0.0013513166795479457</t>
+          <t>0.0015466983938132062 +/- 0.0009002228405961823</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0008923259964307318 +/- 0.0006516627691911591</t>
+          <t>-8.923259964306318e-05 +/- 0.0003271861986912317</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.0019631171921475786 +/- 0.0007430098748838193</t>
+          <t>0.00017846519928612636 +/- 0.0006543723973825088</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.948839976201992e-05 +/- 0.001281419347325285</t>
+          <t>0.001606186793575237 +/- 0.0012492563950029728</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.006930398572278418 +/- 0.0012692794939531207</t>
+          <t>0.0037477691850089424 +/- 0.0016993285969167965</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.0001487209994050831 +/- 0.0009429427414721899</t>
+          <t>-0.0004759071980963703 +/- 0.0005012581661615966</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.003123140987507467 +/- 0.0008226839194491047</t>
+          <t>0.0005651397977394334 +/- 0.0006841165972635292</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.007584770969660937 +/- 0.001919595812047888</t>
+          <t>0.007674003569303989 +/- 0.0009480890809345148</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.0021415823914336606 +/- 0.0006489418271645239</t>
+          <t>0.0007733491969066031 +/- 0.0006937479946276598</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0005651397977394668 +/- 0.0007807498363121057</t>
+          <t>-0.00035693039857226383 +/- 0.0007261484601864386</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0024390243902439267 +/- 0.0012393020021415513</t>
+          <t>0.002141582391433672 +/- 0.0007013578895033644</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.000832837596668623 +/- 0.001150450898620696</t>
+          <t>0.00047590719809635916 +/- 0.0009882955220604408</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.008536585365853677 +/- 0.0012195121951219586</t>
+          <t>0.004491374182034502 +/- 0.0013979773944080868</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.007376561570493734 +/- 0.001462011389344989</t>
+          <t>-0.006573468173706132 +/- 0.0013979773944080742</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.003361094586555602 +/- 0.0011826826503314083</t>
+          <t>0.003063652587745369 +/- 0.0011446687331882102</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0038667459845330376 +/- 0.0014388324357463226</t>
+          <t>0.004878048780487787 +/- 0.0011611672394969109</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0015764425936942382 +/- 0.0019186738159274364</t>
+          <t>0.002290303390838777 +/- 0.0007875194702482996</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.000951814396192785 +/- 0.0005452201897627444</t>
+          <t>0.00041641879833431705 +/- 0.0006124705616292036</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0004164187983342948 +/- 0.001082296573388494</t>
+          <t>0.003361094586555624 +/- 0.001226745426966172</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.007555026769779904 +/- 0.0021986577766301275</t>
+          <t>0.012522308149910765 +/- 0.0021176951232989246</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.005264723378941061 +/- 0.0011291048718680883</t>
+          <t>-0.002439024390243916 +/- 0.0016171656417689826</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.0016359309934562583 +/- 0.002637859465534936</t>
+          <t>-0.004907792980368831 +/- 0.001130670898795251</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.0006841165972635066 +/- 0.00042169681376435754</t>
+          <t>-0.0019631171921475456 +/- 0.0004646192549617419</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.00017846519928612636 +/- 0.00040346995735424037</t>
+          <t>-0.00017846519928613747 +/- 0.000518607845751403</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>5.948839976206432e-05 +/- 0.000320354836831335</t>
+          <t>2.9744199881021062e-05 +/- 0.00016017741841564892</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.006424747174300982 +/- 0.0021082742589731665</t>
+          <t>-0.004461629982153492 +/- 0.001021746819590572</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.001011302795954816 +/- 0.001624806696460166</t>
+          <t>0.005324211778703158 +/- 0.0018596667498323074</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,147 +5176,147 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.001279000594884039 +/- 0.0006657652970136778</t>
+          <t>-0.00029744199881023283 +/- 0.0006095747035074279</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.002171326591314737 +/- 0.0011676256053771957</t>
+          <t>-0.0008923259964306984 +/- 0.0012965196143785373</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.0027067221891730942 +/- 0.0021176951232989333</t>
+          <t>-0.004312908982748398 +/- 0.0016196256264202206</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.0013682331945270465 +/- 0.0010147960802636624</t>
+          <t>-0.00026769779892921175 +/- 0.0004300069094229924</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.003004164187983371 +/- 0.0015764425936942309</t>
+          <t>0.0037775133848899634 +/- 0.0006789239863482039</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0.0012195121951219634 +/- 0.0016261673923660645</t>
+          <t>-0.005502676977989307 +/- 0.0013581737128888591</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0011897679952409534 +/- 0.0015626324255281058</t>
+          <t>0.001814396192742429 +/- 0.001653146131063681</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.0021415823914336498 +/- 0.0014376021384407596</t>
+          <t>0.0028256989886972115 +/- 0.0007784802098930606</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>8.923259964306318e-05 +/- 0.0001904558071812132</t>
+          <t>0.0002379535990481685 +/- 0.00017846519928612639</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0003271861986912317 +/- 0.0012650904412930997</t>
+          <t>0.001487209994051153 +/- 0.001401453776251021</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.003569303985722805 +/- 0.0010641608459249518</t>
+          <t>0.0030041641879833604 +/- 0.0014779605293045674</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.00044616299821533814 +/- 0.0006550480531096279</t>
+          <t>-5.9488399762042124e-05 +/- 0.0010025163323231774</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.0034503271861987318 +/- 0.0015294420145368637</t>
+          <t>0.0037180249851279214 +/- 0.001114911648660982</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0006841165972635177 +/- 0.0016670025305415778</t>
+          <t>-0.0027662105889351583 +/- 0.001369848773309874</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.0013384889946460698 +/- 0.0011691400361114423</t>
+          <t>0.0017549077929803758 +/- 0.0007218715704647078</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>5.9488399762042124e-05 +/- 0.0002225852103970061</t>
+          <t>-0.00020820939916715853 +/- 0.0003271861986912549</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.0005948839976204878 +/- 0.0006379420163452481</t>
+          <t>-0.00026769779892922286 +/- 0.0005056513979774057</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-2.9744199880998856e-05 +/- 0.000696928882442605</t>
+          <t>-0.001457465794170143 +/- 0.0008666747343446464</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-0.00017846519928612636 +/- 0.00014571622503170743</t>
+          <t>-0.00011897679952408425 +/- 0.00023795359904816847</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0012195121951219744 +/- 0.0005556675101805312</t>
+          <t>0.0006246281975014866 +/- 0.0007095098418724887</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.002974419988102306 +/- 0.0013168318632467923</t>
+          <t>0.0009220701963117195 +/- 0.0009541353320847956</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0002676977989291895 +/- 8.923259964306317e-05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0008923259964307318 +/- 0.00037623767521336105</t>
+          <t>0.0006246281975014645 +/- 0.00040891514232206525</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.003450327186198665 +/- 0.0011838042083362312</t>
+          <t>5.948839976203102e-05 +/- 0.0009292385099234616</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0007733491969066364 +/- 0.001755663838592936</t>
+          <t>0.0031826293872694754 +/- 0.0011446687331881967</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0020226055919096097 +/- 0.0008178302846441184</t>
+          <t>0.00041641879833430594 +/- 0.000380911614362449</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.00261748958953002 +/- 0.0013154874709991667</t>
+          <t>0.0027662105889351583 +/- 0.0009220701963117122</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.0002974419988101995 +/- 0.0018238797997330222</t>
+          <t>-0.001397977394408101 +/- 0.0007291880233272723</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.004550862581796577 +/- 0.0007647210072684451</t>
+          <t>0.0027364663890541265 +/- 0.0007959005449291997</t>
         </is>
       </c>
     </row>
